--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -21,9 +21,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_and_Method'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Verification'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Updated_Table_2'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Updated_Table_4'!$A$1:$C$16</definedName>
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Project 1 update through Jul 2026</t>
+          <t>Project 1 update through Aug 2026</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T13:41:56</t>
+          <t>2026-09-15T17:26:51</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3715046783874216</v>
+        <v>0.3688166062876869</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.473577226931443</v>
+        <v>9.489110087902208</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.5241488622315456</v>
+        <v>0.518969354785811</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.714654012384022</v>
+        <v>6.743637841110598</v>
       </c>
     </row>
     <row r="3">
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.552270603645037</v>
+        <v>3.534642216788909</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3882041321353366</v>
+        <v>0.3857634519698406</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.150522391674688</v>
+        <v>9.162719274570497</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5791256161049186</v>
+        <v>0.5751283038247289</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.133851628834669</v>
+        <v>6.14583249212874</v>
       </c>
     </row>
     <row r="4">
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02530998899887851</v>
+        <v>-0.02668390169468571</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.08305537019862617</v>
+        <v>0.08276917989976497</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.3047363335850518</v>
+        <v>-0.32238934500741</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1058495973296158</v>
+        <v>0.1057831234614072</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2391127565659335</v>
+        <v>-0.2522510285340628</v>
       </c>
     </row>
   </sheetData>
@@ -765,21 +765,21 @@
         <v>46.57265489959113</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03263370241484307</v>
+        <v>0.03245415728861997</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.01293292530011</v>
+        <v>46.70649053326548</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.85293292530012</v>
+        <v>11.54649053326548</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -798,21 +798,21 @@
         <v>12.80668196833166</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009824109332120233</v>
+        <v>0.009968591383249884</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.44724565179176</v>
+        <v>12.64046028511974</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.077245651791761</v>
+        <v>4.270460285119738</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -828,24 +828,24 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82295882614039</v>
+        <v>27.82298177528853</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01982792636944819</v>
+        <v>0.02043076663695832</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.56767522253958</v>
+        <v>27.46839945977315</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.377675222539576</v>
+        <v>6.278399459773151</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2613,8 +2613,23 @@
         <v>0.0339</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0.0123</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C116"/>
+  <autoFilter ref="A1:C117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2625,7 +2640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2712,7 +2727,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2763,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2799,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2835,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2871,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2907,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2943,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2979,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3015,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3051,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3087,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3123,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3195,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3231,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3267,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3303,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3339,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3375,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3411,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3447,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3483,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3519,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3555,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3591,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3627,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3663,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3699,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3735,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3771,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3807,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3843,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3879,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3915,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3951,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3987,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4023,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4059,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4095,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4131,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4167,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4203,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4239,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4275,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4311,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4347,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4383,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4419,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4455,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4491,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4527,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4563,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4599,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4635,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4671,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4707,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4743,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4779,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4815,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4851,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4887,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4923,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4959,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4995,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5031,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5067,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5103,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5139,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5175,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5211,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5247,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5283,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5319,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5355,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5391,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5427,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5463,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5499,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5535,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5571,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5607,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5643,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5679,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5715,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5751,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5787,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5823,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5859,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5895,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5931,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5967,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6003,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6039,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6075,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6111,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6147,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6183,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6219,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6255,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6291,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6327,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6363,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6399,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6435,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6471,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6507,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6543,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6579,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6615,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6651,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6687,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6723,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6759,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6795,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6831,48 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>16763.419921875</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>17219.939453125</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0.0272330785351429</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H116"/>
+  <autoFilter ref="A1:H117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6832,7 +6883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6904,7 +6955,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.62549090385437</v>
+        <v>2.622556209564209</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6912,14 +6963,14 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68250560760498</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285938558352174</v>
+        <v>0.0228591470497912</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6991,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68250560760498</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6948,14 +6999,14 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499260425567627</v>
+        <v>2.496466398239136</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935283243179036</v>
+        <v>-0.06935277556863939</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6976,7 +7027,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499260425567627</v>
+        <v>2.496466398239136</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6984,14 +7035,14 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739734649658</v>
+        <v>2.67974066734314</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0734134415145471</v>
+        <v>0.07341347323291636</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7063,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739734649658</v>
+        <v>2.67974066734314</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -7020,14 +7071,14 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.565841436386108</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250421205546351</v>
+        <v>-0.04250382596535285</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7099,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.565841436386108</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7056,14 +7107,14 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558812379837036</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854462412563477</v>
+        <v>0.3854459413790421</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7135,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558812379837036</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7092,14 +7143,14 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.56398868560791</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454503699099385</v>
+        <v>0.001454655740082078</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7171,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.56398868560791</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7128,14 +7179,14 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006528854370117</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699140486252</v>
+        <v>0.1241696717852019</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7207,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006528854370117</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7164,14 +7215,14 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356164383561634</v>
+        <v>0.04356189773556429</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7243,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7200,14 +7251,14 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411285400390625</v>
+        <v>4.40635347366333</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506392446076891</v>
+        <v>0.05506341882685883</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7279,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411285400390625</v>
+        <v>4.40635347366333</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7236,14 +7287,14 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.097486972808838</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568497101328961</v>
+        <v>0.1568493093612204</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7315,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.097486972808838</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7272,14 +7323,14 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956111431121826</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882171416760748</v>
+        <v>-0.02882105628470177</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7351,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956111431121826</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7308,14 +7359,14 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.772735595703125</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592256053872533</v>
+        <v>-0.03592239798838426</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7387,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.772735595703125</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7344,14 +7395,14 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.062729358673096</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702841717105691</v>
+        <v>0.2702839361416431</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7423,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.062729358673096</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7380,14 +7431,14 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979395866394043</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484755857082565</v>
+        <v>-0.01484773445048615</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7459,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979395866394043</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7416,14 +7467,14 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722181797027588</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.0430167319765653</v>
+        <v>-0.04301657298715189</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7495,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722181797027588</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7452,14 +7503,14 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556883811950684</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888723059494003</v>
+        <v>-0.02888710249012416</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7531,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556883811950684</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7488,14 +7539,14 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.228055953979492</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363097163717</v>
+        <v>0.1220360864374244</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7567,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.228055953979492</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7524,14 +7575,14 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857003688812256</v>
+        <v>5.850456237792969</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062873724857742</v>
+        <v>-0.06062882526693603</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7603,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857003688812256</v>
+        <v>5.850456237792969</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7560,14 +7611,14 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.047036647796631</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360051231671157</v>
+        <v>0.03360086837908227</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7639,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.047036647796631</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7596,14 +7647,14 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.94319486618042</v>
+        <v>6.935433864593506</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.146914757174905</v>
+        <v>0.1469144753935934</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7675,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.94319486618042</v>
+        <v>6.935433864593506</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7632,14 +7683,14 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211391988220623</v>
+        <v>0.001211166243223705</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7711,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7668,14 +7719,14 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215311527252197</v>
+        <v>5.209483623504639</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497688045483735</v>
+        <v>-0.2497683912712815</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7747,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215311527252197</v>
+        <v>5.209483623504639</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -7704,14 +7755,14 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.046820640563965</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240500650023255</v>
+        <v>-0.2240500045812026</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7783,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.046820640563965</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7740,14 +7791,14 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831363842994731</v>
+        <v>-0.183136818674309</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7819,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7776,14 +7827,14 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677881889603055</v>
+        <v>0.07677904068510788</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7855,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7812,14 +7863,14 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.819417715072632</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421897082719897</v>
+        <v>0.07421900381634172</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7891,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.819417715072632</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7848,14 +7899,14 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640088082323901</v>
+        <v>0.1640089866296075</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7927,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7884,14 +7935,14 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486505031585693</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019797673586959</v>
+        <v>0.008019546108555708</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7963,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486505031585693</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7920,14 +7971,14 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.357765674591064</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507481493818129</v>
+        <v>-0.2507479491647804</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7999,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.357765674591064</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -7956,14 +8007,14 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.070911407470703</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123879532281372</v>
+        <v>0.2123869864642927</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7984,7 +8035,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.070911407470703</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -7992,14 +8043,14 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186889171600342</v>
+        <v>4.182209491729736</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733922257928567</v>
+        <v>0.02733984435396586</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8071,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186889171600342</v>
+        <v>4.182209491729736</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -8028,14 +8079,14 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160976886749268</v>
+        <v>4.156326770782471</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188911095817207</v>
+        <v>-0.006188767205097756</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8107,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160976886749268</v>
+        <v>4.156326770782471</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -8064,14 +8115,14 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.319096088409424</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.0391620591824553</v>
+        <v>0.03916181922248385</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8143,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.319096088409424</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8100,14 +8151,14 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.987789630889893</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548229768248279</v>
+        <v>0.154822566757649</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8128,7 +8179,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.987789630889893</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8136,14 +8187,14 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899645736355199</v>
+        <v>0.07899683685315129</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8215,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8172,14 +8223,14 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563282285618801</v>
+        <v>0.08563278232560179</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8251,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -8208,14 +8259,14 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877295970916748</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802197433110722</v>
+        <v>0.004802348231823794</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8287,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877295970916748</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8244,14 +8295,14 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.710042476654053</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429664625194604</v>
+        <v>0.1429661787258361</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8323,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.710042476654053</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8280,14 +8331,14 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395680836540848</v>
+        <v>-0.02395654513128542</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8359,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8316,14 +8367,14 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.26999044418335</v>
+        <v>7.261864185333252</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088013721369481</v>
+        <v>0.1088012308531945</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8395,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.26999044418335</v>
+        <v>7.261864185333252</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8352,14 +8403,14 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830543518066406</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146568260115995</v>
+        <v>0.214656969264309</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8431,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830543518066406</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8388,14 +8439,14 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.453957557678223</v>
+        <v>9.443387031555176</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059747096386237</v>
+        <v>0.07059699667439601</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8467,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.453957557678223</v>
+        <v>9.443387031555176</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8424,14 +8475,14 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176066076792814</v>
+        <v>0.1176071683315141</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8503,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8460,14 +8511,14 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282806396484</v>
+        <v>13.29794979095459</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599917862993668</v>
+        <v>0.2599918060250836</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8539,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282806396484</v>
+        <v>13.29794979095459</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8496,14 +8547,14 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47214031219482</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196682233590973</v>
+        <v>0.01196672870330273</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8575,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47214031219482</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8532,14 +8583,14 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47994041442871</v>
+        <v>12.465989112854</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364827523864081</v>
+        <v>-0.07364847598012692</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8611,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47994041442871</v>
+        <v>12.465989112854</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8568,14 +8619,14 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.3436975479126</v>
+        <v>13.32878017425537</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921163922267226</v>
+        <v>0.06921160074748678</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8647,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.3436975479126</v>
+        <v>13.32878017425537</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8604,14 +8655,14 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253009796143</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556768457364667</v>
+        <v>-0.02556732179522692</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8683,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253009796143</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8640,14 +8691,14 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998041314080548</v>
+        <v>-0.004998199561433103</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8719,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8676,14 +8727,14 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65938091278076</v>
+        <v>13.64411449432373</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579405627172118</v>
+        <v>0.05579413045721027</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8755,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65938091278076</v>
+        <v>13.64411449432373</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8712,14 +8763,14 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.0263693823436163</v>
+        <v>-0.02636960049531378</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8791,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8748,14 +8799,14 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.93761920928955</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544633344791</v>
+        <v>0.1244545437838092</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8827,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.93761920928955</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8784,14 +8835,14 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479347229004</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.0822810403859966</v>
+        <v>0.08228130993934912</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8863,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479347229004</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8820,14 +8871,14 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355560302734</v>
+        <v>19.91127014160156</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316224879332291</v>
+        <v>0.2316219541977889</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8899,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355560302734</v>
+        <v>19.91127014160156</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8856,14 +8907,14 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517193695026387</v>
+        <v>-0.02517175579831477</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8935,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8892,14 +8943,14 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31177139282227</v>
+        <v>22.28683471679688</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482098192612498</v>
+        <v>0.1482099974588429</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8971,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31177139282227</v>
+        <v>22.28683471679688</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8928,14 +8979,14 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.62515830993652</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455892965801925</v>
+        <v>-0.07455865437939457</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8956,7 +9007,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.62515830993652</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -8964,14 +9015,14 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341668407136812</v>
+        <v>0.2341664229132356</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8992,7 +9043,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -9000,14 +9051,14 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.53269577026367</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537130761895</v>
+        <v>0.2780535014795418</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9079,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.53269577026367</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -9036,14 +9087,14 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.0998100797688396</v>
+        <v>-0.09980991413127971</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9115,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -9072,14 +9123,14 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40888595581055</v>
+        <v>24.3816089630127</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.167454434811324</v>
+        <v>-0.1674542959030992</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9151,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40888595581055</v>
+        <v>24.3816089630127</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9108,14 +9159,14 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820846557617</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124624549298961</v>
+        <v>-0.004124858161063338</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9187,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820846557617</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9144,14 +9195,14 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571079042555</v>
+        <v>0.1191571387757528</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9223,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9180,14 +9231,14 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.47107696533203</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741339540492</v>
+        <v>-0.3202739802562728</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9259,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.47107696533203</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -9216,14 +9267,14 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61636924743652</v>
+        <v>18.59556198120117</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739661008697384</v>
+        <v>0.006739456291735557</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9295,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61636924743652</v>
+        <v>18.59556198120117</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9252,14 +9303,14 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.10013675689697</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709813357917</v>
+        <v>-0.1879709377881579</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9331,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.10013675689697</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9288,14 +9339,14 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.19816581003128</v>
+        <v>0.1981658545877099</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9367,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9324,14 +9375,14 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.03538513183594</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689697973216241</v>
+        <v>-0.1689699318887956</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9403,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.03538513183594</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9360,14 +9411,14 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.09545421600342</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955340888197248</v>
+        <v>-0.1955341276631157</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9439,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.09545421600342</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9396,14 +9447,14 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363258361816</v>
+        <v>13.44858360290527</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708414046692</v>
+        <v>0.1118709031291722</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9475,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363258361816</v>
+        <v>13.44858360290527</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9432,14 +9483,14 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.88548278808594</v>
+        <v>16.86660766601562</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541550494055593</v>
+        <v>0.254154947765054</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9511,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.88548278808594</v>
+        <v>16.86660766601562</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -9468,14 +9519,14 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5653018951416</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415619095126</v>
+        <v>-0.1364415308901092</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9547,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5653018951416</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -9504,14 +9555,14 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.47190284729004</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368687351278623</v>
+        <v>0.3368691557148624</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9583,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.47190284729004</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9540,14 +9591,14 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16453170776367</v>
+        <v>23.13863563537598</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883094302655908</v>
+        <v>0.1883089093471031</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9619,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16453170776367</v>
+        <v>23.13863563537598</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9576,14 +9627,14 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012138366699</v>
+        <v>27.68914222717285</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966622823795958</v>
+        <v>0.1966627014446669</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9655,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012138366699</v>
+        <v>27.68914222717285</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9612,14 +9663,14 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.00100795915484464</v>
+        <v>-0.001008053614069193</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9691,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9648,14 +9699,14 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.75653076171875</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365332711422</v>
+        <v>0.363436428780211</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9727,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.75653076171875</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9684,14 +9735,14 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105081934617</v>
+        <v>0.1182106865009505</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9763,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9720,14 +9771,14 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.58600997924805</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046523499921483</v>
+        <v>0.1046520284189869</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9799,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.58600997924805</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -9756,14 +9807,14 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619638947121319</v>
+        <v>0.05619655619364927</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9835,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9792,14 +9843,14 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185780952231065</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9871,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9828,14 +9879,14 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.70406341552734</v>
+        <v>40.65856170654297</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250716057470163</v>
+        <v>-0.062507267540302</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9907,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.70406341552734</v>
+        <v>40.65856170654297</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -9864,14 +9915,14 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.63073348999023</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468858589700071</v>
+        <v>0.1468859579084962</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9943,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.63073348999023</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9900,14 +9951,14 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43413162231445</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893412834461786</v>
+        <v>0.05893414142888309</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9979,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43413162231445</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9936,14 +9987,14 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175241944488</v>
+        <v>0.2424175564739466</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9964,7 +10015,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -9972,14 +10023,14 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97162628173828</v>
+        <v>78.88337707519531</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858094213803009</v>
+        <v>0.2858097587910202</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10051,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97162628173828</v>
+        <v>78.88337707519531</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -10008,14 +10059,14 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421812779074114</v>
+        <v>0.1421810468342366</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10087,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -10044,14 +10095,14 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.25273895263672</v>
+        <v>86.15634155273438</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.0437602868993443</v>
+        <v>-0.04376022325813289</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10123,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.25273895263672</v>
+        <v>86.15634155273438</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -10080,14 +10131,14 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4435958862305</v>
+        <v>109.3212738037109</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688709624204324</v>
+        <v>0.2688708902152934</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10159,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4435958862305</v>
+        <v>109.3212738037109</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10116,14 +10167,14 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367309570312</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269433351334972</v>
+        <v>0.1269432152707823</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10144,7 +10195,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367309570312</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10152,14 +10203,14 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.8274383544922</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277659422323111</v>
+        <v>-0.05277657397651536</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10231,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.8274383544922</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -10188,14 +10239,14 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008212771048568</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10267,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -10224,14 +10275,14 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.1150207519531</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742813318985359</v>
+        <v>0.01742808690201669</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10303,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.1150207519531</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10260,14 +10311,14 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.4047546386719</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321460769799583</v>
+        <v>0.09321497710709581</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10339,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.4047546386719</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10296,14 +10347,14 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135301258146518</v>
+        <v>0.04135259928286272</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10375,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -10332,14 +10383,14 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691468412549</v>
+        <v>-0.02857691133769347</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10411,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10368,14 +10419,14 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902751059577</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10447,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -10404,14 +10455,14 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039318634820721</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10483,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10440,14 +10491,14 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.2283248901367</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323250437332495</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10519,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.2283248901367</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -10476,14 +10527,14 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982410811787075</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10555,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.64599609375</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -10512,14 +10563,14 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.2406354069759602</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10591,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10548,14 +10599,14 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.603515625</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516823827925</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10627,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.603515625</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -10584,14 +10635,14 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258305979143173</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10663,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10620,14 +10671,14 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10699,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10656,14 +10707,14 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10735,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -10692,14 +10743,14 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.0852717678839181</v>
+        <v>0.08527167560685012</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10771,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -10728,14 +10779,14 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.125882777513319</v>
+        <v>-0.1258827644807442</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10807,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -10764,14 +10815,14 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.05373099736807707</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10792,7 +10843,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -10800,14 +10851,14 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482579447315181</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10879,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -10836,14 +10887,14 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293465552553402</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10864,7 +10915,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -10872,14 +10923,14 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925510196515</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10951,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -10908,14 +10959,14 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234085538123</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10987,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -10944,14 +10995,14 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>210.8942108154297</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797465881657349</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10972,7 +11023,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>210.8942108154297</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -10980,14 +11031,14 @@
         </is>
       </c>
       <c r="F115" s="3" t="n">
-        <v>200.0899963378906</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>-0.05123049341072095</v>
+        <v>-0.05123052301166586</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11059,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>200.0899963378906</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -11016,19 +11067,55 @@
         </is>
       </c>
       <c r="F116" s="3" t="n">
-        <v>200.75</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0.003298534030631073</v>
+        <v>0.003298560492809743</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>200.5256195068359</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>220.5332336425781</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0.09977585001332034</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H116"/>
+  <autoFilter ref="A1:H117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11113,17 +11200,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.06349317981017011</v>
+        <v>2.72330785351429</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.06349317981017011</v>
+        <v>2.72330785351429</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.06349317981017011</v>
+        <v>2.72330785351429</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -11135,7 +11222,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11152,17 +11239,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.3298534030631073</v>
+        <v>9.977585001332034</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3298534030631073</v>
+        <v>9.977585001332034</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3298534030631073</v>
+        <v>9.977585001332034</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -11174,7 +11261,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11282,7 @@
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11222,10 +11309,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.295628487903424</v>
+        <v>1.307936068641449</v>
       </c>
     </row>
     <row r="3">
@@ -11235,10 +11322,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448012329545969</v>
+        <v>3.42868537831944</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.194520884974981</v>
+        <v>1.207602368089744</v>
       </c>
     </row>
     <row r="4">
@@ -11248,10 +11335,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.65217391304348</v>
+        <v>95.68965517241379</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>69.56521739130434</v>
+        <v>69.82758620689656</v>
       </c>
     </row>
     <row r="5">
@@ -11261,10 +11348,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.347826086956522</v>
+        <v>4.310344827586207</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30.43478260869566</v>
+        <v>30.17241379310345</v>
       </c>
     </row>
     <row r="6">
@@ -11274,10 +11361,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909092</v>
+        <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.616317163875842</v>
+        <v>3.605292357575083</v>
       </c>
     </row>
     <row r="7">
@@ -11326,10 +11413,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.295628487903424</v>
+        <v>1.307936068641449</v>
       </c>
     </row>
     <row r="11">
@@ -11339,10 +11426,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.983943837120484</v>
+        <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.510533237481414</v>
+        <v>4.492835307894532</v>
       </c>
     </row>
     <row r="12">
@@ -11352,10 +11439,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182456</v>
+        <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4323133842228444</v>
+        <v>-0.4416507937681062</v>
       </c>
     </row>
     <row r="13">
@@ -11365,10 +11452,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.54330321288962</v>
+        <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5443369456982423</v>
+        <v>0.5738724008555964</v>
       </c>
     </row>
     <row r="14">
@@ -11378,10 +11465,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349508</v>
+        <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2872450816096581</v>
+        <v>0.2911159610821309</v>
       </c>
     </row>
     <row r="15">
@@ -11391,10 +11478,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287689</v>
+        <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4658018365243973</v>
+        <v>0.4722666723968901</v>
       </c>
     </row>
     <row r="16">
@@ -11404,10 +11491,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612905</v>
+        <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.061929277735463</v>
+        <v>2.081338762374768</v>
       </c>
     </row>
     <row r="17">
@@ -11417,7 +11504,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.552270603645037</v>
+        <v>3.534642216788909</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -11430,7 +11517,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02530998899887851</v>
+        <v>-0.02668390169468571</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -11453,7 +11540,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11480,10 +11567,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.720955800193191</v>
+        <v>4.766270954987323</v>
       </c>
     </row>
     <row r="3">
@@ -11493,10 +11580,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448012329545969</v>
+        <v>3.42868537831944</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.843133091484296</v>
+        <v>3.894525960227657</v>
       </c>
     </row>
     <row r="4">
@@ -11506,10 +11593,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.65217391304348</v>
+        <v>95.68965517241379</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.34782608695652</v>
+        <v>64.65517241379311</v>
       </c>
     </row>
     <row r="5">
@@ -11519,10 +11606,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.347826086956522</v>
+        <v>4.310344827586207</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.65217391304348</v>
+        <v>35.3448275862069</v>
       </c>
     </row>
     <row r="6">
@@ -11532,10 +11619,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909092</v>
+        <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.20774600360396</v>
+        <v>12.17800676700963</v>
       </c>
     </row>
     <row r="7">
@@ -11548,7 +11635,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787493767707</v>
+        <v>-8.791782359687629</v>
       </c>
     </row>
     <row r="8">
@@ -11561,7 +11648,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54462412563478</v>
+        <v>38.54459413790421</v>
       </c>
     </row>
     <row r="9">
@@ -11574,7 +11661,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741339540493</v>
+        <v>-32.02739802562728</v>
       </c>
     </row>
     <row r="10">
@@ -11584,10 +11671,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.720955800193191</v>
+        <v>4.766270954987323</v>
       </c>
     </row>
     <row r="11">
@@ -11597,10 +11684,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.983943837120484</v>
+        <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.45428494013697</v>
+        <v>13.40454352252829</v>
       </c>
     </row>
     <row r="12">
@@ -11610,10 +11697,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182456</v>
+        <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.0217036217385676</v>
+        <v>-0.03153827838289425</v>
       </c>
     </row>
     <row r="13">
@@ -11623,10 +11710,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.54330321288962</v>
+        <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.147212041724103</v>
+        <v>0.1667139613486102</v>
       </c>
     </row>
     <row r="14">
@@ -11636,10 +11723,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349508</v>
+        <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.350888644115867</v>
+        <v>0.355571299162624</v>
       </c>
     </row>
     <row r="15">
@@ -11649,10 +11736,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287689</v>
+        <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6671086457840698</v>
+        <v>0.6764342599160132</v>
       </c>
     </row>
     <row r="16">
@@ -11662,10 +11749,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612905</v>
+        <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.506144831481828</v>
+        <v>2.533825421920513</v>
       </c>
     </row>
   </sheetData>
@@ -11718,13 +11805,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.552270603645037</v>
+        <v>3.534642216788909</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3882041321353366</v>
+        <v>0.3857634519698406</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.150522391674688</v>
+        <v>9.162719274570497</v>
       </c>
     </row>
     <row r="3">
@@ -11734,13 +11821,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02530998899887851</v>
+        <v>-0.02668390169468571</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.08305537019862617</v>
+        <v>0.08276917989976497</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.3047363335850518</v>
+        <v>-0.32238934500741</v>
       </c>
     </row>
   </sheetData>
@@ -11761,7 +11848,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -11799,16 +11886,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3518264189608743</v>
+        <v>0.3509970274106829</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.0001322452612779038</v>
+        <v>0.0001284846804513028</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5.670595079073489e-05</v>
+        <v>6.361355649042701e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6.444721769888872e-05</v>
+        <v>0.0001080691514194616</v>
       </c>
     </row>
     <row r="3">
@@ -11818,16 +11905,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.140188581203098</v>
+        <v>-0.1408993197056948</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1277568081678591</v>
+        <v>0.1242446882228043</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4457248592970162</v>
+        <v>0.4275470952219309</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3066839911331234</v>
+        <v>0.2921222183482972</v>
       </c>
     </row>
     <row r="4">
@@ -11837,16 +11924,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01465478878200355</v>
+        <v>0.01354931980108134</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8735038164340262</v>
+        <v>0.8824833815391561</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9787208520808429</v>
+        <v>0.9765260962819015</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8799447076786946</v>
+        <v>0.904341090705725</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T17:26:51</t>
+          <t>2026-09-20T16:40:04</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82298177528853</v>
+        <v>27.82296061656442</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>116</v>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02043076663695832</v>
+        <v>0.02043075292818304</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.46839945977315</v>
+        <v>27.46837891038678</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.278399459773151</v>
+        <v>6.278378910386781</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.622556209564209</v>
+        <v>2.622556447982788</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.68250560760498</v>
+        <v>2.682507038116455</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0228591470497912</v>
+        <v>0.0228595995254095</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.68250560760498</v>
+        <v>2.682507038116455</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.496466398239136</v>
+        <v>2.49646782875061</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935277556863939</v>
+        <v>-0.06935273858460167</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.496466398239136</v>
+        <v>2.49646782875061</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.67974066734314</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341347323291636</v>
+        <v>0.07341314465886306</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.67974066734314</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565841436386108</v>
+        <v>2.565841197967529</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250382596535285</v>
+        <v>-0.04250417050352995</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565841436386108</v>
+        <v>2.565841197967529</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834127426147</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854459413790421</v>
+        <v>0.3854458842745316</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834127426147</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454655740082078</v>
+        <v>0.001454723004039815</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.002050876617432</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241696717852019</v>
+        <v>0.1241698810152463</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.002050876617432</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.176387310028076</v>
+        <v>4.176388263702393</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356189773556429</v>
+        <v>0.04356201169344254</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.176387310028076</v>
+        <v>4.176388263702393</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>4.40635347366333</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506341882685883</v>
+        <v>0.05506317790412329</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097486972808838</v>
+        <v>5.097490310668945</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568493093612204</v>
+        <v>0.1568500668719666</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097486972808838</v>
+        <v>5.097490310668945</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571060180664</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882105628470177</v>
+        <v>-0.02882187930417091</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571060180664</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772735595703125</v>
+        <v>4.772735118865967</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592239798838426</v>
+        <v>-0.03592230858882117</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772735595703125</v>
+        <v>4.772735118865967</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.062729358673096</v>
+        <v>6.062732696533203</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702839361416431</v>
+        <v>0.2702847624139151</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.062729358673096</v>
+        <v>6.062732696533203</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484773445048615</v>
+        <v>-0.01484819817920868</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786457061768</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301657298715189</v>
+        <v>-0.04301656955288269</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786457061768</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.550673484802246</v>
+        <v>5.550672054290771</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888710249012416</v>
+        <v>-0.02888743377860092</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.550673484802246</v>
+        <v>5.550672054290771</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228055953979492</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220360864374244</v>
+        <v>0.1220366333256104</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228055953979492</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850456237792969</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062882526693603</v>
+        <v>-0.06062896446669497</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850456237792969</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047036647796631</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360086837908227</v>
+        <v>0.03360053962341936</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047036647796631</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935433864593506</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469144753935934</v>
+        <v>0.146914667857688</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935433864593506</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835258483887</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211166243223705</v>
+        <v>0.001211441341556485</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835258483887</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.209483623504639</v>
+        <v>5.209482192993164</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497683912712815</v>
+        <v>-0.249768751839513</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.209483623504639</v>
+        <v>5.209482192993164</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042298793792725</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240500045812026</v>
+        <v>-0.2240498830397153</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042298793792725</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.302005052566528</v>
+        <v>3.302004814147949</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.183136818674309</v>
+        <v>-0.1831367812965286</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.302005052566528</v>
+        <v>3.302004814147949</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530071258545</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677904068510788</v>
+        <v>0.07677919063725391</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530071258545</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417715072632</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421900381634172</v>
+        <v>0.07421899883953387</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417715072632</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>4.445836544036865</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640089866296075</v>
+        <v>0.1640089139689633</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481488704681396</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019546108555708</v>
+        <v>0.008019224344257836</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481488704681396</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765674591064</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507479491647804</v>
+        <v>-0.2507477632008893</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765674591064</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -8007,10 +8007,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070911407470703</v>
+        <v>4.070912837982178</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123869864642927</v>
+        <v>0.212387498580785</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070911407470703</v>
+        <v>4.070912837982178</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>4.182209491729736</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733984435396586</v>
+        <v>0.02733948334858605</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.156326770782471</v>
+        <v>4.156326293945312</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188767205097756</v>
+        <v>-0.006188881220705822</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.156326770782471</v>
+        <v>4.156326293945312</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.319096088409424</v>
+        <v>4.319095134735107</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916181922248385</v>
+        <v>0.03916170898971694</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.319096088409424</v>
+        <v>4.319095134735107</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987789630889893</v>
+        <v>4.987791061401367</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.154822566757649</v>
+        <v>0.1548231529536039</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987789630889893</v>
+        <v>4.987791061401367</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381811618804932</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899683685315129</v>
+        <v>0.07899700539838994</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381811618804932</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842668533325195</v>
+        <v>5.842667579650879</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563278232560179</v>
+        <v>0.08563212417834198</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842668533325195</v>
+        <v>5.842667579650879</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>5.870727062225342</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802348231823794</v>
+        <v>0.004802512241529833</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710042476654053</v>
+        <v>6.710043430328369</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661787258361</v>
+        <v>0.1429663411715274</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710042476654053</v>
+        <v>6.710043430328369</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395654513128542</v>
+        <v>-0.0239566127896278</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>7.261864185333252</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012308531945</v>
+        <v>0.1088011501242385</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443387031555176</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059699667439601</v>
+        <v>0.07059732102863103</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443387031555176</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>10.55399703979492</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176071683315141</v>
+        <v>0.1176068297349091</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.32878017425537</v>
+        <v>13.328782081604</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921160074748678</v>
+        <v>0.06921175375168209</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.32878017425537</v>
+        <v>13.328782081604</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799705505371</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556732179522692</v>
+        <v>-0.02556760433653082</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799705505371</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998199561433103</v>
+        <v>-0.004998053440725236</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8727,10 +8727,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.64411449432373</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579413045721027</v>
+        <v>0.05579390906862258</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.64411449432373</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636960049531378</v>
+        <v>-0.02636918664632026</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93761920928955</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545437838092</v>
+        <v>0.1244544451908152</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93761920928955</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>16.16670608520508</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228130993934912</v>
+        <v>0.08228117174547189</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.41006851196289</v>
+        <v>19.41006660461426</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517175579831477</v>
+        <v>-0.02517185159072888</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.41006851196289</v>
+        <v>19.41006660461426</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683471679688</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099974588429</v>
+        <v>0.1482103068206888</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683471679688</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.62515830993652</v>
+        <v>20.62515258789062</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455865437939457</v>
+        <v>-0.07455906952685742</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.62515830993652</v>
+        <v>20.62515258789062</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341664229132356</v>
+        <v>0.2341669502622643</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.53269577026367</v>
+        <v>32.53270721435547</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780535014795418</v>
+        <v>0.2780537595323853</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.53269577026367</v>
+        <v>32.53270721435547</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>29.28561019897461</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09980991413127971</v>
+        <v>-0.09981023079284457</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.3816089630127</v>
+        <v>24.38160514831543</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542959030992</v>
+        <v>-0.1674544261615176</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.3816089630127</v>
+        <v>24.38160514831543</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9159,10 +9159,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28104019165039</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124858161063338</v>
+        <v>-0.004124624119425047</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28104019165039</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.17429733276367</v>
+        <v>27.17430114746094</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571387757528</v>
+        <v>0.1191572079686052</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.17429733276367</v>
+        <v>27.17430114746094</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>18.47107696533203</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202739802562728</v>
+        <v>-0.3202740756754329</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59556198120117</v>
+        <v>18.59556007385254</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739456291735557</v>
+        <v>0.006739353030370099</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59556198120117</v>
+        <v>18.59556007385254</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013675689697</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709377881579</v>
+        <v>-0.1879709570683575</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013675689697</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09246826171875</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981658545877099</v>
+        <v>0.1981662585587558</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09246826171875</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538513183594</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689699318887956</v>
+        <v>-0.1689700016846472</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538513183594</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>12.09545421600342</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341276631157</v>
+        <v>-0.1955342297154857</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.5653018951416</v>
+        <v>14.56530094146729</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415308901092</v>
+        <v>-0.1364415874322625</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.5653018951416</v>
+        <v>14.56530094146729</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47190284729004</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368691557148624</v>
+        <v>0.3368688503927728</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47190284729004</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9591,10 +9591,10 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863563537598</v>
+        <v>23.13863754272461</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883089093471031</v>
+        <v>0.1883093564995657</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863563537598</v>
+        <v>23.13863754272461</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68914222717285</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966627014446669</v>
+        <v>0.1966625203708421</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68914222717285</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9663,10 +9663,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008053614069193</v>
+        <v>-0.001007915914793878</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71432876586914</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.363436428780211</v>
+        <v>0.3634364726737245</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71432876586914</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182106865009505</v>
+        <v>0.1182105733971262</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.20398330688477</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619655619364927</v>
+        <v>0.05619663807868869</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.20398330688477</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36948013305664</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780952231065</v>
+        <v>-0.1185779309735295</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36948013305664</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9879,10 +9879,10 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.65856170654297</v>
+        <v>40.6585693359375</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.062507267540302</v>
+        <v>-0.06250733900434413</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.65856170654297</v>
+        <v>40.6585693359375</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.63073348999023</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468859579084962</v>
+        <v>0.1468856488778802</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.63073348999023</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.37887573242188</v>
+        <v>49.37887954711914</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893414142888309</v>
+        <v>0.05893430986310011</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.37887573242188</v>
+        <v>49.37887954711914</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175564739466</v>
+        <v>0.2424175377463125</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -10023,10 +10023,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.88337707519531</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858097587910202</v>
+        <v>0.2858094301189487</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.88337707519531</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>90.09909820556641</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421810468342366</v>
+        <v>0.1421812677718244</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212738037109</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688708902152934</v>
+        <v>0.2688710673211081</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212738037109</v>
+        <v>109.3212890625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269432152707823</v>
+        <v>0.1269429881861628</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277657397651536</v>
+        <v>-0.05277645338988224</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008212771048568</v>
+        <v>0.02008206101966881</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150207519531</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742808690201669</v>
+        <v>0.0174281509928309</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150207519531</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047546386719</v>
+        <v>132.4047393798828</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321497710709581</v>
+        <v>0.09321478225631852</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047546386719</v>
+        <v>132.4047393798828</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>137.8800354003906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135259928286272</v>
+        <v>0.04135271929200823</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10383,10 +10383,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398651123047</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691133769347</v>
+        <v>-0.02857680067055435</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398651123047</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901794305278</v>
+        <v>-0.1058902812899192</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039318634820721</v>
+        <v>0.04039305893354816</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323250437332495</v>
+        <v>-0.1323248762370933</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982481462220356</v>
+        <v>0.004982410538207693</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348754882812</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258305979143173</v>
+        <v>0.125830694731885</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348754882812</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.0207454681313487</v>
+        <v>-0.02074546634730989</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125119707459349</v>
+        <v>0.07125110299903326</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258827644807442</v>
+        <v>-0.1258826889444383</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373099736807707</v>
+        <v>0.05373090631056576</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -10887,10 +10887,10 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293472316669725</v>
+        <v>-0.07293464314527709</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -10923,10 +10923,10 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925888464382</v>
+        <v>-0.01569258749190239</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234709050238</v>
+        <v>0.1443234582488593</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797470065579535</v>
+        <v>0.05797461957992356</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.766270954987323</v>
+        <v>4.766271550373824</v>
       </c>
     </row>
     <row r="3">
@@ -11583,7 +11583,7 @@
         <v>3.42868537831944</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.894525960227657</v>
+        <v>3.894525878804123</v>
       </c>
     </row>
     <row r="4">
@@ -11622,7 +11622,7 @@
         <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.17800676700963</v>
+        <v>12.17801071817231</v>
       </c>
     </row>
     <row r="7">
@@ -11635,7 +11635,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791782359687629</v>
+        <v>-8.791787902916088</v>
       </c>
     </row>
     <row r="8">
@@ -11648,7 +11648,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54459413790421</v>
+        <v>38.54458842745316</v>
       </c>
     </row>
     <row r="9">
@@ -11661,7 +11661,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02739802562728</v>
+        <v>-32.02740756754329</v>
       </c>
     </row>
     <row r="10">
@@ -11674,7 +11674,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.766270954987323</v>
+        <v>4.766271550373824</v>
       </c>
     </row>
     <row r="11">
@@ -11687,7 +11687,7 @@
         <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.40454352252829</v>
+        <v>13.40454892611204</v>
       </c>
     </row>
     <row r="12">
@@ -11700,7 +11700,7 @@
         <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03153827838289425</v>
+        <v>-0.03153799374004402</v>
       </c>
     </row>
     <row r="13">
@@ -11713,7 +11713,7 @@
         <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1667139613486102</v>
+        <v>0.1667112763682104</v>
       </c>
     </row>
     <row r="14">
@@ -11726,7 +11726,7 @@
         <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.355571299162624</v>
+        <v>0.355571200243011</v>
       </c>
     </row>
     <row r="15">
@@ -11739,7 +11739,7 @@
         <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6764342599160132</v>
+        <v>0.6764341416878362</v>
       </c>
     </row>
     <row r="16">
@@ -11752,7 +11752,7 @@
         <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.533825421920513</v>
+        <v>2.533824646442687</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20T16:40:04</t>
+          <t>2026-09-25T17:44:36</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296061656442</v>
+        <v>27.82296363114063</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>116</v>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02043075292818304</v>
+        <v>0.02043075488133247</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.46837891038678</v>
+        <v>27.46838183814793</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.278378910386781</v>
+        <v>6.278381838147926</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.682507038116455</v>
+        <v>2.682506084442139</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0228595995254095</v>
+        <v>0.02285923588240113</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.682507038116455</v>
+        <v>2.682506084442139</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.49646782875061</v>
+        <v>2.496467113494873</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935273858460167</v>
+        <v>-0.06935267436157733</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.49646782875061</v>
+        <v>2.496467113494873</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.679741382598877</v>
+        <v>2.679741621017456</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341314465886306</v>
+        <v>0.07341354770182096</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.679741382598877</v>
+        <v>2.679741621017456</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565841197967529</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250417050352995</v>
+        <v>-0.04250443363410483</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565841197967529</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834127426147</v>
+        <v>3.554833889007568</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854458842745316</v>
+        <v>0.3854460488262499</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834127426147</v>
+        <v>3.554833889007568</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.56000542640686</v>
+        <v>3.560005903244019</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454723004039815</v>
+        <v>0.001454924308121219</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.56000542640686</v>
+        <v>3.560005903244019</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.002050876617432</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241698810152463</v>
+        <v>0.1241695964979852</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.002050876617432</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.176388263702393</v>
+        <v>4.176385402679443</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356201169344254</v>
+        <v>0.04356142114270756</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.176388263702393</v>
+        <v>4.176385402679443</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.40635347366333</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506317790412329</v>
+        <v>0.05506412902187185</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.40635347366333</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097490310668945</v>
+        <v>5.097488880157471</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568500668719666</v>
+        <v>0.1568494918456691</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097490310668945</v>
+        <v>5.097488880157471</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>4.950571060180664</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882187930417091</v>
+        <v>-0.02882160676185097</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772735118865967</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592230858882117</v>
+        <v>-0.03592211594956707</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772735118865967</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.062732696533203</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702847624139151</v>
+        <v>0.2702840090465197</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.062732696533203</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.97271203994751</v>
+        <v>5.972712516784668</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484819817920868</v>
+        <v>-0.01484773211492074</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.97271203994751</v>
+        <v>5.972712516784668</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>5.715786457061768</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301656955288269</v>
+        <v>-0.04301664595456089</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.550672054290771</v>
+        <v>5.550674438476562</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888743377860092</v>
+        <v>-0.02888701665563653</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.550672054290771</v>
+        <v>5.550674438476562</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220366333256104</v>
+        <v>0.1220359795639541</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850456714630127</v>
+        <v>5.850455284118652</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062896446669497</v>
+        <v>-0.06062905031329091</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850456714630127</v>
+        <v>5.850455284118652</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047036170959473</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360053962341936</v>
+        <v>0.0336009553605936</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047036170959473</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.146914667857688</v>
+        <v>0.1469146446878671</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>6.943835258483887</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211441341556485</v>
+        <v>0.001211303667462804</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.209482192993164</v>
+        <v>5.20948314666748</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.249768751839513</v>
+        <v>-0.2497686144983635</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.209482192993164</v>
+        <v>5.20948314666748</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042297840118408</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240498830397153</v>
+        <v>-0.224050116621593</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042297840118408</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.302004814147949</v>
+        <v>3.302005767822266</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831367812965286</v>
+        <v>-0.1831364490139741</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.302004814147949</v>
+        <v>3.302005767822266</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555530071258545</v>
+        <v>3.555530309677124</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677919063725391</v>
+        <v>0.07677895184963979</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555530071258545</v>
+        <v>3.555530309677124</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819417238235474</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421899883953387</v>
+        <v>0.07421872563992093</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819417238235474</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445836544036865</v>
+        <v>4.445834159851074</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640089139689633</v>
+        <v>0.1640085077232876</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445836544036865</v>
+        <v>4.445834159851074</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481488704681396</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019224344257836</v>
+        <v>0.008020086683348415</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481488704681396</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507477632008893</v>
+        <v>-0.2507480555662548</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -8007,10 +8007,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070912837982178</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.212387498580785</v>
+        <v>0.2123877266768006</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070912837982178</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182209491729736</v>
+        <v>4.182210445404053</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733948334858605</v>
+        <v>0.02733959727896007</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182209491729736</v>
+        <v>4.182210445404053</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>4.156326293945312</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188881220705822</v>
+        <v>-0.006189107840612107</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.319095134735107</v>
+        <v>4.31909704208374</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916170898971694</v>
+        <v>0.03916216789224225</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.319095134735107</v>
+        <v>4.31909704208374</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>4.987791061401367</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548231529536039</v>
+        <v>0.1548226429742401</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381811618804932</v>
+        <v>5.381809711456299</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899700539838994</v>
+        <v>0.07899662299491528</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381811618804932</v>
+        <v>5.381809711456299</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>5.842667579650879</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563212417834198</v>
+        <v>0.08563250893348173</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802512241529833</v>
+        <v>0.004802349015690988</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>6.710043430328369</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429663411715274</v>
+        <v>0.142966526841515</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.0239566127896278</v>
+        <v>-0.02395668385282779</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.261864185333252</v>
+        <v>7.261863708496094</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088011501242385</v>
+        <v>0.1088011580457702</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.261864185333252</v>
+        <v>7.261863708496094</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.820673942565918</v>
+        <v>8.820672988891602</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.214656969264309</v>
+        <v>0.2146569176961779</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.820673942565918</v>
+        <v>8.820672988891602</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443391799926758</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059732102863103</v>
+        <v>0.07059765301574861</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443391799926758</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8475,10 +8475,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399703979492</v>
+        <v>10.55399608612061</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176068297349091</v>
+        <v>0.1176065030154168</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399703979492</v>
+        <v>10.55399608612061</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.29794979095459</v>
+        <v>13.29795074462891</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599918060250836</v>
+        <v>0.2599920102412046</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.29794979095459</v>
+        <v>13.29795074462891</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.45708274841309</v>
+        <v>13.4570837020874</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196672870330273</v>
+        <v>0.01196672784509833</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.45708274841309</v>
+        <v>13.4570837020874</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>12.465989112854</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364847598012692</v>
+        <v>-0.07364854162864898</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32878112792969</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921175375168209</v>
+        <v>0.06921167724958432</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32878112792969</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799705505371</v>
+        <v>12.98799991607666</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556760433653082</v>
+        <v>-0.0255673199658849</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799705505371</v>
+        <v>12.98799991607666</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308139801025</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998053440725236</v>
+        <v>-0.004998346049113311</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308139801025</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>13.64411163330078</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579390906862258</v>
+        <v>0.05579398698220239</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432750701904</v>
+        <v>13.28432559967041</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636918664632026</v>
+        <v>-0.02636932643912504</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432750701904</v>
+        <v>13.28432559967041</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762016296387</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544451908152</v>
+        <v>0.1244545348492871</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762016296387</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228117174547189</v>
+        <v>0.08228136852999035</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8871,10 +8871,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.91127014160156</v>
+        <v>19.9112720489502</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316219541977889</v>
+        <v>0.2316219268710247</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.91127014160156</v>
+        <v>19.9112720489502</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.41006660461426</v>
+        <v>19.41007041931152</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517185159072888</v>
+        <v>-0.0251717533870518</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.41006660461426</v>
+        <v>19.41007041931152</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683853149414</v>
+        <v>22.28683662414551</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482103068206888</v>
+        <v>0.1482099828948495</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683853149414</v>
+        <v>22.28683662414551</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>20.62515258789062</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455906952685742</v>
+        <v>-0.07455899032591362</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341669502622643</v>
+        <v>0.2341667653086137</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.53270721435547</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537595323853</v>
+        <v>0.2780538012018414</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.53270721435547</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -9087,10 +9087,10 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981023079284457</v>
+        <v>-0.09981006661035974</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.38160514831543</v>
+        <v>24.38160705566406</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674544261615176</v>
+        <v>-0.1674544152553439</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.38160514831543</v>
+        <v>24.38160705566406</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9159,10 +9159,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28104019165039</v>
+        <v>24.28103256225586</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124624119425047</v>
+        <v>-0.004125014941738225</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28104019165039</v>
+        <v>24.28103256225586</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.17430114746094</v>
+        <v>27.1742992401123</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572079686052</v>
+        <v>0.1191574810683276</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.17430114746094</v>
+        <v>27.1742992401123</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.47107696533203</v>
+        <v>18.47107315063477</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740756754329</v>
+        <v>-0.3202741683447206</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.47107696533203</v>
+        <v>18.47107315063477</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59556007385254</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739353030370099</v>
+        <v>0.006739767467747848</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59556007385254</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013198852539</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709570683575</v>
+        <v>-0.1879712775032717</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013198852539</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09247016906738</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981662585587558</v>
+        <v>0.1981663592620166</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09247016906738</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.03538608551025</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689700016846472</v>
+        <v>-0.168969966786725</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.03538608551025</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9411,10 +9411,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.09545421600342</v>
+        <v>12.09545516967773</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955342297154857</v>
+        <v>-0.195534115260649</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.09545421600342</v>
+        <v>12.09545516967773</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>13.44858360290527</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118709031291722</v>
+        <v>0.1118708154629613</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.86660766601562</v>
+        <v>16.86660385131836</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.254154947765054</v>
+        <v>0.2541546641145687</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.86660766601562</v>
+        <v>16.86660385131836</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>14.56530094146729</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415874322625</v>
+        <v>-0.1364413921224097</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368688503927728</v>
+        <v>0.3368689813443158</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>23.13863754272461</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883093564995657</v>
+        <v>0.1883092401000188</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68914031982422</v>
+        <v>27.68913841247559</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625203708421</v>
+        <v>0.1966624379395134</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68914031982422</v>
+        <v>27.68913841247559</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007915914793878</v>
+        <v>-0.00100784709986157</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432495117188</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364726737245</v>
+        <v>0.3634361968582969</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432495117188</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105733971262</v>
+        <v>0.118210698457627</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>46.58600997924805</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046520284189869</v>
+        <v>0.1046521283397153</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36948013305664</v>
+        <v>43.36947250366211</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779309735295</v>
+        <v>-0.1185780860299585</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36948013305664</v>
+        <v>43.36947250366211</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9879,10 +9879,10 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.6585693359375</v>
+        <v>40.65856552124023</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250733900434413</v>
+        <v>-0.06250726204228019</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.6585693359375</v>
+        <v>40.65856552124023</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307258605957</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468856488778802</v>
+        <v>0.1468856626590918</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307258605957</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>49.37887954711914</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893430986310011</v>
+        <v>0.05893439649082755</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34917831420898</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175377463125</v>
+        <v>0.2424173832390697</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34917831420898</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858094301189487</v>
+        <v>0.285809590022434</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -10059,10 +10059,10 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09909057617188</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421812677718244</v>
+        <v>0.1421811710544132</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09909057617188</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.15634155273438</v>
+        <v>86.15633392333984</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376022325813289</v>
+        <v>-0.04376022696365323</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.15634155273438</v>
+        <v>86.15633392333984</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710673211081</v>
+        <v>0.2688710911304248</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429881861628</v>
+        <v>0.1269431366228349</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>116.6968612670898</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277645338988224</v>
+        <v>-0.05277651204904255</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174281509928309</v>
+        <v>0.01742821508364489</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047393798828</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321478225631852</v>
+        <v>0.09321458740556565</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047393798828</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>137.8800354003906</v>
+        <v>137.8800201416016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135271929200823</v>
+        <v>0.04135272405764212</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>137.8800354003906</v>
+        <v>137.8800201416016</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -10383,10 +10383,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398651123047</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680067055435</v>
+        <v>-0.02857680383306749</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398651123047</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902812899192</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942840576172</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039305893354816</v>
+        <v>0.04039318634820721</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942840576172</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>108.1073608398438</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323248762370933</v>
+        <v>-0.1323249824993521</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10563,10 +10563,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406354069759602</v>
+        <v>0.24063554742098</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10599,10 +10599,10 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.603515625</v>
+        <v>157.6035003662109</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516823827925</v>
+        <v>0.169251436814627</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.603515625</v>
+        <v>157.6035003662109</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>177.4348754882812</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.125830694731885</v>
+        <v>0.1258308037320852</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074546634730989</v>
+        <v>-0.02074555234387065</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125110299903326</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.08527167560685012</v>
+        <v>0.08527175758426342</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258826889444383</v>
+        <v>-0.1258827549720258</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.766271550373824</v>
+        <v>4.766271304346992</v>
       </c>
     </row>
     <row r="3">
@@ -11622,7 +11622,7 @@
         <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.17801071817231</v>
+        <v>12.17801022895345</v>
       </c>
     </row>
     <row r="7">
@@ -11635,7 +11635,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787902916088</v>
+        <v>-8.791787704079452</v>
       </c>
     </row>
     <row r="8">
@@ -11648,7 +11648,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54458842745316</v>
+        <v>38.54460488262499</v>
       </c>
     </row>
     <row r="9">
@@ -11661,7 +11661,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740756754329</v>
+        <v>-32.02741683447206</v>
       </c>
     </row>
     <row r="10">
@@ -11674,7 +11674,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.766271550373824</v>
+        <v>4.766271304346992</v>
       </c>
     </row>
     <row r="11">
@@ -11687,7 +11687,7 @@
         <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.40454892611204</v>
+        <v>13.4045464149397</v>
       </c>
     </row>
     <row r="12">
@@ -11700,7 +11700,7 @@
         <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03153799374004402</v>
+        <v>-0.03153888819748991</v>
       </c>
     </row>
     <row r="13">
@@ -11713,7 +11713,7 @@
         <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1667112763682104</v>
+        <v>0.1667138987122159</v>
       </c>
     </row>
     <row r="14">
@@ -11726,7 +11726,7 @@
         <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.355571200243011</v>
+        <v>0.3555712485007971</v>
       </c>
     </row>
     <row r="15">
@@ -11739,7 +11739,7 @@
         <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6764341416878362</v>
+        <v>0.6764340386298822</v>
       </c>
     </row>
     <row r="16">
@@ -11752,7 +11752,7 @@
         <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.533824646442687</v>
+        <v>2.533824601958516</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -21,9 +21,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_and_Method'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$117</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$117</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Verification'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Updated_Table_2'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Updated_Table_4'!$A$1:$C$16</definedName>
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Project 1 update through Aug 2026</t>
+          <t>Project 1 update through Sept 2026</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T17:44:36</t>
+          <t>2026-10-10T17:36:40</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145302</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3688166062876869</v>
+        <v>0.3662303402743725</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.489110087902208</v>
+        <v>9.499882769239695</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.518969354785811</v>
+        <v>0.5149206796216128</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.743637841110598</v>
+        <v>6.756662602290388</v>
       </c>
     </row>
     <row r="3">
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.534642216788909</v>
+        <v>3.511429319936214</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3857634519698406</v>
+        <v>0.3828516705792904</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.162719274570497</v>
+        <v>9.171774840692462</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5751283038247289</v>
+        <v>0.5698893582375369</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.14583249212874</v>
+        <v>6.161598333395458</v>
       </c>
     </row>
     <row r="4">
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02668390169468571</v>
+        <v>-0.02495282129216941</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.08276917989976497</v>
+        <v>0.08249578451452012</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.32238934500741</v>
+        <v>-0.3024738953513129</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1057831234614072</v>
+        <v>0.1057404898472523</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2522510285340628</v>
+        <v>-0.23598170699053</v>
       </c>
     </row>
   </sheetData>
@@ -765,21 +765,21 @@
         <v>46.57265489959113</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sept 2026</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03245415728861997</v>
+        <v>0.03226541457697028</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>46.70649053326548</v>
+        <v>46.38498135854536</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.54649053326548</v>
+        <v>11.22498135854536</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -798,21 +798,21 @@
         <v>12.80668196833166</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sept 2026</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009968591383249884</v>
+        <v>0.009852249259162317</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.64046028511974</v>
+        <v>12.48485309971457</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.270460285119738</v>
+        <v>4.114853099714567</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -828,24 +828,24 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296363114063</v>
+        <v>27.82295574656268</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sept 2026</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02043075488133247</v>
+        <v>0.0205531804479008</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.46838183814793</v>
+        <v>27.65201829092905</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.278381838147926</v>
+        <v>6.462018290929048</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2628,8 +2628,23 @@
         <v>0.0123</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Sept 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0.0109</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C117"/>
+  <autoFilter ref="A1:C118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2640,7 +2655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2727,7 +2742,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2778,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2814,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2850,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2886,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2922,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2958,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2994,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3030,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3066,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3102,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3138,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3174,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3210,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3246,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3282,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3318,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3354,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3390,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3426,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3462,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3498,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3534,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3570,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3606,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3642,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3678,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3714,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3750,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3786,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3822,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3858,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3894,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3930,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3966,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4002,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4038,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4074,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4110,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4146,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4182,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4218,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4254,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4290,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4326,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4362,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4398,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4434,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4470,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4506,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4542,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4578,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4614,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4650,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4686,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4722,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4758,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4794,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4830,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4866,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4902,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4938,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4974,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4995,7 +5010,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5046,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5082,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5118,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5154,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5190,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5226,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5262,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5298,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5334,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5370,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5406,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5442,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5478,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5514,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5550,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5586,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5622,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5658,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5694,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5730,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5766,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5802,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5838,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5874,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5910,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5946,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5982,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6018,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6054,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6090,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6126,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6162,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6198,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6234,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6270,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6306,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6342,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6378,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6414,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6450,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6486,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6522,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6558,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6594,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6630,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6666,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6702,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6738,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6774,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6810,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6846,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6882,48 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Sept 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>17219.939453125</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>17160.41015625</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>-0.003456998036319825</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H117"/>
+  <autoFilter ref="A1:H118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6883,7 +6934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6963,14 +7014,14 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.682506084442139</v>
+        <v>2.682506799697876</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285923588240113</v>
+        <v>0.02285950861465746</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6991,7 +7042,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.682506084442139</v>
+        <v>2.682506799697876</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7002,11 +7053,11 @@
         <v>2.496467113494873</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935267436157733</v>
+        <v>-0.06935292250664793</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7035,14 +7086,14 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.679741621017456</v>
+        <v>2.679741144180298</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341354770182096</v>
+        <v>0.0734133566970383</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7114,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.679741621017456</v>
+        <v>2.679741144180298</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -7074,11 +7125,11 @@
         <v>2.565840721130371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250443363410483</v>
+        <v>-0.04250426325590773</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7107,14 +7158,14 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554833889007568</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854460488262499</v>
+        <v>0.3854463275870208</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7186,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554833889007568</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7143,14 +7194,14 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560005903244019</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454924308121219</v>
+        <v>0.001454655740082078</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7222,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560005903244019</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7179,14 +7230,14 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.00205135345459</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241695964979852</v>
+        <v>0.1241699396708196</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7258,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.00205135345459</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7218,11 +7269,11 @@
         <v>4.176385402679443</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356142114270756</v>
+        <v>0.04356117246580737</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7251,14 +7302,14 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406353950500488</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506412902187185</v>
+        <v>0.05506401484726586</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7330,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406353950500488</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7290,11 +7341,11 @@
         <v>5.097488880157471</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568494918456691</v>
+        <v>0.1568496170350731</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7323,14 +7374,14 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.950571060180664</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882160676185097</v>
+        <v>-0.0288214196747697</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7402,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.950571060180664</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7359,14 +7410,14 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772733688354492</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592211594956707</v>
+        <v>-0.03592278326681819</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7438,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772733688354492</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7395,14 +7446,14 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.062730312347412</v>
+        <v>6.06273078918457</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840090465197</v>
+        <v>0.2702847435166309</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7474,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.062730312347412</v>
+        <v>6.06273078918457</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7431,14 +7482,14 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.972712516784668</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484773211492074</v>
+        <v>-0.01484796689881163</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7510,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.972712516784668</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7467,14 +7518,14 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715786457061768</v>
+        <v>5.715785503387451</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301664595456089</v>
+        <v>-0.04301665282311129</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7546,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715786457061768</v>
+        <v>5.715785503387451</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7503,14 +7554,14 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.550674438476562</v>
+        <v>5.55067253112793</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888701665563653</v>
+        <v>-0.02888718832462622</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7582,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.550674438476562</v>
+        <v>5.55067253112793</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7539,14 +7590,14 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.22805643081665</v>
+        <v>6.228055000305176</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220359795639541</v>
+        <v>0.122036107404736</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7618,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.22805643081665</v>
+        <v>6.228055000305176</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7575,14 +7626,14 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850455284118652</v>
+        <v>5.850455760955811</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062905031329091</v>
+        <v>-0.0606287579879855</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7654,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850455284118652</v>
+        <v>5.850455760955811</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7614,11 +7665,11 @@
         <v>6.047036170959473</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.0336009553605936</v>
+        <v>0.03360087111769672</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7647,14 +7698,14 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935434341430664</v>
+        <v>6.935434818267822</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469146446878671</v>
+        <v>0.1469147235425563</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7726,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935434341430664</v>
+        <v>6.935434818267822</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7683,14 +7734,14 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.943835258483887</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211303667462804</v>
+        <v>0.001211028569177319</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7762,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.943835258483887</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7722,11 +7773,11 @@
         <v>5.20948314666748</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497686144983635</v>
+        <v>-0.2497684599418704</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7755,14 +7806,14 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042297840118408</v>
+        <v>4.042296886444092</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.224050116621593</v>
+        <v>-0.2240502996866476</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7834,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042297840118408</v>
+        <v>4.042296886444092</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7794,11 +7845,11 @@
         <v>3.302005767822266</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831364490139741</v>
+        <v>-0.1831362562963657</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7827,14 +7878,14 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555530309677124</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677895184963979</v>
+        <v>0.07677880744130383</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7906,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555530309677124</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7863,14 +7914,14 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417238235474</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421872563992093</v>
+        <v>0.07421907087205204</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7942,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417238235474</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7899,14 +7950,14 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445834159851074</v>
+        <v>4.445835590362549</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640085077232876</v>
+        <v>0.1640086642779561</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7978,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445834159851074</v>
+        <v>4.445835590362549</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7935,14 +7986,14 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481491088867188</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008020086683348415</v>
+        <v>0.008019976847981169</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7963,7 +8014,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481491088867188</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7971,14 +8022,14 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765197753906</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480555662548</v>
+        <v>-0.2507481618085182</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8050,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765197753906</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -8007,14 +8058,14 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123877266768006</v>
+        <v>0.2123872145602557</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8086,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -8043,14 +8094,14 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182210445404053</v>
+        <v>4.182209968566895</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733959727896007</v>
+        <v>0.0273398411515744</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8122,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182210445404053</v>
+        <v>4.182209968566895</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -8082,11 +8133,11 @@
         <v>4.156326293945312</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189107840612107</v>
+        <v>-0.006188994530671899</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8115,14 +8166,14 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.31909704208374</v>
+        <v>4.319095611572266</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916216789224225</v>
+        <v>0.03916182371534838</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8194,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.31909704208374</v>
+        <v>4.319095611572266</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8151,14 +8202,14 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987791061401367</v>
+        <v>4.987790584564209</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548226429742401</v>
+        <v>0.1548229150566363</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8230,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987791061401367</v>
+        <v>4.987790584564209</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8187,14 +8238,14 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381809711456299</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899662299491528</v>
+        <v>0.07899691734969516</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8266,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381809711456299</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8223,14 +8274,14 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842667579650879</v>
+        <v>5.842669486999512</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563250893348173</v>
+        <v>0.08563267096236871</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8302,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842667579650879</v>
+        <v>5.842669486999512</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -8259,14 +8310,14 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870726108551025</v>
+        <v>5.870726585388184</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802349015690988</v>
+        <v>0.00480210260927838</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8338,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870726108551025</v>
+        <v>5.870726585388184</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8295,14 +8346,14 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710043430328369</v>
+        <v>6.710044384002686</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.142966526841515</v>
+        <v>0.1429665964522182</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8374,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710043430328369</v>
+        <v>6.710044384002686</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8334,11 +8385,11 @@
         <v>6.549293041229248</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395668385282779</v>
+        <v>-0.02395682257433085</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8425,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8403,14 +8454,14 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.820672988891602</v>
+        <v>8.820675849914551</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146569176961779</v>
+        <v>0.2146573116753359</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8482,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.820672988891602</v>
+        <v>8.820675849914551</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8439,14 +8490,14 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443391799926758</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059765301574861</v>
+        <v>0.07059708952683108</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8518,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443391799926758</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8475,14 +8526,14 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399608612061</v>
+        <v>10.55399799346924</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176065030154168</v>
+        <v>0.117606930723466</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8554,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399608612061</v>
+        <v>10.55399799346924</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8514,11 +8565,11 @@
         <v>13.29795074462891</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599920102412046</v>
+        <v>0.2599917825318532</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8547,14 +8598,14 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.4570837020874</v>
+        <v>13.45708179473877</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196672784509833</v>
+        <v>0.01196658441332676</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8626,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.4570837020874</v>
+        <v>13.45708179473877</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8586,11 +8637,11 @@
         <v>12.465989112854</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364854162864898</v>
+        <v>-0.07364841033159564</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8619,14 +8670,14 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.32878112792969</v>
+        <v>13.328782081604</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921167724958432</v>
+        <v>0.06921175375168209</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8698,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.32878112792969</v>
+        <v>13.328782081604</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8655,14 +8706,14 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799991607666</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255673199658849</v>
+        <v>-0.02556746123653708</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8734,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799991607666</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8691,14 +8742,14 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.92308139801025</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998346049113311</v>
+        <v>-0.004998199561433103</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8770,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.92308139801025</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8727,14 +8778,14 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.64411163330078</v>
+        <v>13.6441125869751</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579398698220239</v>
+        <v>0.0557939828648184</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8806,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.64411163330078</v>
+        <v>13.6441125869751</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8763,14 +8814,14 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432559967041</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636932643912504</v>
+        <v>-0.02636946438879895</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8842,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432559967041</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8799,14 +8850,14 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762016296387</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545348492871</v>
+        <v>0.1244546873627026</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8878,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762016296387</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8838,11 +8889,11 @@
         <v>16.16670799255371</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228136852999035</v>
+        <v>0.08228129943304796</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8929,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8965,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8950,7 +9001,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8979,14 +9030,14 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.62515258789062</v>
+        <v>20.62515449523926</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455899032591362</v>
+        <v>-0.07455890474406701</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9058,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.62515258789062</v>
+        <v>20.62515449523926</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -9015,14 +9066,14 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341667653086137</v>
+        <v>0.2341668361304334</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9094,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -9051,14 +9102,14 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53271102905273</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780538012018414</v>
+        <v>0.2780539093935128</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9130,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53271102905273</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -9087,14 +9138,14 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.28561210632324</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981006661035974</v>
+        <v>-0.09981033634665004</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9166,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.28561210632324</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -9126,11 +9177,11 @@
         <v>24.38160705566406</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674544152553439</v>
+        <v>-0.1674543610323084</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9159,14 +9210,14 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103256225586</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004125014941738225</v>
+        <v>-0.004124858483746885</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9238,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103256225586</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9198,11 +9249,11 @@
         <v>27.1742992401123</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191574810683276</v>
+        <v>0.119157305241937</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9231,14 +9282,14 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.47107315063477</v>
+        <v>18.47107124328613</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741683447206</v>
+        <v>-0.3202742385341527</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9310,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.47107315063477</v>
+        <v>18.47107124328613</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -9267,14 +9318,14 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.5955638885498</v>
+        <v>18.59555816650391</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739767467747848</v>
+        <v>0.006739561640910274</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9346,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.5955638885498</v>
+        <v>18.59555816650391</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9303,14 +9354,14 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013198852539</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879712775032717</v>
+        <v>-0.1879708737784411</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9382,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013198852539</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9339,14 +9390,14 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247016906738</v>
+        <v>18.09247398376465</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981663592620166</v>
+        <v>0.1981663848721067</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9418,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247016906738</v>
+        <v>18.09247398376465</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9378,11 +9429,11 @@
         <v>15.03538608551025</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.168969966786725</v>
+        <v>-0.1689701420047741</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9469,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9447,14 +9498,14 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.44858360290527</v>
+        <v>13.44858264923096</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708154629613</v>
+        <v>0.1118707366172873</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9526,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.44858360290527</v>
+        <v>13.44858264923096</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9483,14 +9534,14 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.86660385131836</v>
+        <v>16.86660575866699</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541546641145687</v>
+        <v>0.2541548948752226</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9562,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.86660385131836</v>
+        <v>16.86660575866699</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -9519,14 +9570,14 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.56530094146729</v>
+        <v>14.56530284881592</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364413921224097</v>
+        <v>-0.1364413766930278</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9598,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.56530094146729</v>
+        <v>14.56530284881592</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -9555,14 +9606,14 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189903259277</v>
+        <v>19.47189521789551</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368689813443158</v>
+        <v>0.3368685443762311</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9634,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189903259277</v>
+        <v>19.47189521789551</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9591,14 +9642,14 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863754272461</v>
+        <v>23.13863372802734</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883092401000188</v>
+        <v>0.1883092769912784</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9619,7 +9670,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863754272461</v>
+        <v>23.13863372802734</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9627,14 +9678,14 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68913841247559</v>
+        <v>27.68914413452148</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966624379395134</v>
+        <v>0.1966628825185215</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9706,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68913841247559</v>
+        <v>27.68914413452148</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9666,11 +9717,11 @@
         <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.00100784709986157</v>
+        <v>-0.001008053544630072</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9699,14 +9750,14 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71432495117188</v>
+        <v>37.71433639526367</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634361968582969</v>
+        <v>0.3634366105814382</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9778,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71432495117188</v>
+        <v>37.71433639526367</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9735,14 +9786,14 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.17256164550781</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.118210698457627</v>
+        <v>0.1182104602933247</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9814,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.17256164550781</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9771,14 +9822,14 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.58600997924805</v>
+        <v>46.58601760864258</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046521283397153</v>
+        <v>0.1046522093279367</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9850,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.58600997924805</v>
+        <v>46.58601760864258</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -9807,14 +9858,14 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.2039794921875</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619663807868869</v>
+        <v>0.05619630133525821</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9886,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.2039794921875</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9846,11 +9897,11 @@
         <v>43.36947250366211</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780860299585</v>
+        <v>-0.1185779493598029</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9937,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9915,14 +9966,14 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.6307258605957</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468856626590918</v>
+        <v>0.1468857564818131</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9994,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.6307258605957</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9951,14 +10002,14 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.37887954711914</v>
+        <v>49.37888336181641</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893439649082755</v>
+        <v>0.05893439166961034</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9979,7 +10030,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.37887954711914</v>
+        <v>49.37888336181641</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9987,14 +10038,14 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34917831420898</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424173832390697</v>
+        <v>0.242417441765066</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10066,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34917831420898</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -10023,14 +10074,14 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.88336181640625</v>
+        <v>78.88335418701172</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.285809590022434</v>
+        <v>0.2858093057587894</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10102,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.88336181640625</v>
+        <v>78.88335418701172</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -10059,14 +10110,14 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.09909057617188</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811710544132</v>
+        <v>0.1421813782406502</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10138,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.09909057617188</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -10098,11 +10149,11 @@
         <v>86.15633392333984</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376022696365323</v>
+        <v>-0.04376030793594532</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10131,14 +10182,14 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710911304248</v>
+        <v>0.2688711796833401</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10210,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10167,14 +10218,14 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431366228349</v>
+        <v>0.1269429881861628</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10246,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10203,14 +10254,14 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968612670898</v>
+        <v>116.6968688964844</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277651204904255</v>
+        <v>-0.05277639146240565</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10282,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968612670898</v>
+        <v>116.6968688964844</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -10239,14 +10290,14 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.0403747558594</v>
+        <v>119.0403671264648</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008206101966881</v>
+        <v>0.02008192895097527</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10318,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.0403747558594</v>
+        <v>119.0403671264648</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -10275,14 +10326,14 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150360107422</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742821508364489</v>
+        <v>0.0174282162006334</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10354,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150360107422</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10311,14 +10362,14 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321458740556565</v>
+        <v>0.09321453028446558</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10390,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10350,11 +10401,11 @@
         <v>137.8800201416016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135272405764212</v>
+        <v>0.04135284406682982</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10383,14 +10434,14 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398345947266</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680383306749</v>
+        <v>-0.02857691450021882</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10462,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398345947266</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10419,14 +10470,14 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.7569351196289</v>
+        <v>119.7569427490234</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901794305278</v>
+        <v>-0.1058900206097576</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10498,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.7569351196289</v>
+        <v>119.7569427490234</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -10455,14 +10506,14 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942916870117</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039318634820721</v>
+        <v>0.0403930563602144</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10534,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942916870117</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10491,14 +10542,14 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249824993521</v>
+        <v>-0.132324990602127</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10570,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -10530,11 +10581,11 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982410538207693</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10563,14 +10614,14 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.7900848388672</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.24063554742098</v>
+        <v>0.2406354069759602</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10642,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.7900848388672</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10602,11 +10653,11 @@
         <v>157.6035003662109</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.169251436814627</v>
+        <v>0.1692515691786884</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10635,14 +10686,14 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348754882812</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258308037320852</v>
+        <v>0.1258307069145082</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10714,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348754882812</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10674,11 +10725,11 @@
         <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555234387065</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10765,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10743,14 +10794,14 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.08527175758426342</v>
+        <v>0.0852718395616765</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10822,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -10782,11 +10833,11 @@
         <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258827549720258</v>
+        <v>-0.1258828209996035</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10873,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10909,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10887,14 +10938,14 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293464314527709</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10966,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -10923,14 +10974,14 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.01569258749190239</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10951,7 +11002,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -10959,14 +11010,14 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234582488593</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10987,7 +11038,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -10998,11 +11049,11 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797461957992356</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11089,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11125,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11110,12 +11161,48 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Sept 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>220.5332336425781</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>228.3800048828125</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0.03558090139353665</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H117"/>
+  <autoFilter ref="A1:H118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11200,17 +11287,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.72330785351429</v>
+        <v>-0.3456998036319825</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2.72330785351429</v>
+        <v>-0.3456998036319825</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.72330785351429</v>
+        <v>-0.3456998036319825</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -11222,7 +11309,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11239,17 +11326,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.977585001332034</v>
+        <v>3.558090139353665</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>9.977585001332034</v>
+        <v>3.558090139353665</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9.977585001332034</v>
+        <v>3.558090139353665</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -11261,7 +11348,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1788566400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1791158400&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11309,10 +11396,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.307936068641449</v>
+        <v>1.293802428707488</v>
       </c>
     </row>
     <row r="3">
@@ -11322,10 +11409,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.42868537831944</v>
+        <v>3.408469136214709</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.207602368089744</v>
+        <v>1.194224232291563</v>
       </c>
     </row>
     <row r="4">
@@ -11335,10 +11422,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.68965517241379</v>
+        <v>95.72649572649573</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>69.82758620689656</v>
+        <v>69.23076923076923</v>
       </c>
     </row>
     <row r="5">
@@ -11348,10 +11435,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.310344827586207</v>
+        <v>4.273504273504273</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30.17241379310345</v>
+        <v>30.76923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -11361,7 +11448,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.696486486486487</v>
+        <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3.605292357575083</v>
@@ -11377,7 +11464,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-4.008802771462106</v>
+        <v>-3.907049911244601</v>
       </c>
     </row>
     <row r="8">
@@ -11413,10 +11500,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.307936068641449</v>
+        <v>1.293802428707488</v>
       </c>
     </row>
     <row r="11">
@@ -11426,10 +11513,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.972276416934467</v>
+        <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.492835307894532</v>
+        <v>4.476039261568972</v>
       </c>
     </row>
     <row r="12">
@@ -11439,10 +11526,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.651927277101982</v>
+        <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4416507937681062</v>
+        <v>-0.4335291363518803</v>
       </c>
     </row>
     <row r="13">
@@ -11452,10 +11539,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.629009524988723</v>
+        <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5738724008555964</v>
+        <v>0.5905376312934969</v>
       </c>
     </row>
     <row r="14">
@@ -11465,10 +11552,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8810417533861374</v>
+        <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2911159610821309</v>
+        <v>0.2890507328244424</v>
       </c>
     </row>
     <row r="15">
@@ -11478,10 +11565,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.56591488300176</v>
+        <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4722666723968901</v>
+        <v>0.4691411362145471</v>
       </c>
     </row>
     <row r="16">
@@ -11491,10 +11578,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.54147465437789</v>
+        <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.081338762374768</v>
+        <v>2.076223234619459</v>
       </c>
     </row>
     <row r="17">
@@ -11504,7 +11591,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.534642216788909</v>
+        <v>3.511429319936214</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -11517,7 +11604,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02668390169468571</v>
+        <v>-0.02495282129216941</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -11540,7 +11627,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11567,10 +11654,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.766271304346992</v>
+        <v>4.755945312720088</v>
       </c>
     </row>
     <row r="3">
@@ -11580,10 +11667,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.42868537831944</v>
+        <v>3.408469136214709</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.894525878804123</v>
+        <v>3.891645733695004</v>
       </c>
     </row>
     <row r="4">
@@ -11593,10 +11680,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.68965517241379</v>
+        <v>95.72649572649573</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.65517241379311</v>
+        <v>64.95726495726495</v>
       </c>
     </row>
     <row r="5">
@@ -11606,10 +11693,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.310344827586207</v>
+        <v>4.273504273504273</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.3448275862069</v>
+        <v>35.04273504273504</v>
       </c>
     </row>
     <row r="6">
@@ -11619,10 +11706,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.696486486486487</v>
+        <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.17801022895345</v>
+        <v>12.06459141507334</v>
       </c>
     </row>
     <row r="7">
@@ -11635,7 +11722,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787704079452</v>
+        <v>-8.791788925788385</v>
       </c>
     </row>
     <row r="8">
@@ -11648,7 +11735,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54460488262499</v>
+        <v>38.54463275870208</v>
       </c>
     </row>
     <row r="9">
@@ -11661,7 +11748,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741683447206</v>
+        <v>-32.02742385341527</v>
       </c>
     </row>
     <row r="10">
@@ -11671,10 +11758,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.766271304346992</v>
+        <v>4.755945312720088</v>
       </c>
     </row>
     <row r="11">
@@ -11684,10 +11771,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.972276416934467</v>
+        <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.4045464149397</v>
+        <v>13.34711369180711</v>
       </c>
     </row>
     <row r="12">
@@ -11697,10 +11784,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.651927277101982</v>
+        <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03153888819748991</v>
+        <v>-0.02931179138729888</v>
       </c>
     </row>
     <row r="13">
@@ -11710,10 +11797,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.629009524988723</v>
+        <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1667138987122159</v>
+        <v>0.1936187715291005</v>
       </c>
     </row>
     <row r="14">
@@ -11723,10 +11810,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8810417533861374</v>
+        <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3555712485007971</v>
+        <v>0.3563276242742608</v>
       </c>
     </row>
     <row r="15">
@@ -11736,10 +11823,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.56591488300176</v>
+        <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6764340386298822</v>
+        <v>0.6778716925034239</v>
       </c>
     </row>
     <row r="16">
@@ -11749,10 +11836,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.54147465437789</v>
+        <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.533824601958516</v>
+        <v>2.543695379374659</v>
       </c>
     </row>
   </sheetData>
@@ -11805,13 +11892,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.534642216788909</v>
+        <v>3.511429319936214</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3857634519698406</v>
+        <v>0.3828516705792904</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.162719274570497</v>
+        <v>9.171774840692462</v>
       </c>
     </row>
     <row r="3">
@@ -11821,13 +11908,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02668390169468571</v>
+        <v>-0.02495282129216941</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.08276917989976497</v>
+        <v>0.08249578451452012</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.32238934500741</v>
+        <v>-0.3024738953513129</v>
       </c>
     </row>
   </sheetData>
@@ -11849,7 +11936,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11886,16 +11973,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3509970274106829</v>
+        <v>0.352906727312786</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.0001284846804513028</v>
+        <v>0.0001104917251849064</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6.361355649042701e-05</v>
+        <v>6.775773678677842e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0001080691514194616</v>
+        <v>0.0001573140187863196</v>
       </c>
     </row>
     <row r="3">
@@ -11905,16 +11992,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1408993197056948</v>
+        <v>-0.141745700150389</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1242446882228043</v>
+        <v>0.1204437627181503</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4275470952219309</v>
+        <v>0.4242018367818284</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2921222183482972</v>
+        <v>0.2865737320015871</v>
       </c>
     </row>
     <row r="4">
@@ -11924,16 +12011,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01354931980108134</v>
+        <v>0.01420447443690255</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8824833815391561</v>
+        <v>0.8763333571020252</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9765260962819015</v>
+        <v>0.9764233648274664</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.904341090705725</v>
+        <v>0.9051211984022886</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10T17:36:40</t>
+          <t>2026-10-15T17:33:58</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82295574656268</v>
+        <v>27.82296821150432</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>117</v>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0205531804479008</v>
+        <v>0.02055318845689392</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.65201829092905</v>
+        <v>27.65203031222323</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.462018290929048</v>
+        <v>6.462030312223231</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -6943,7 +6943,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -7006,7 +7006,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.622556447982788</v>
+        <v>2.62255597114563</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.682506799697876</v>
+        <v>2.68250584602356</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285950861465746</v>
+        <v>0.02285933094947112</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.682506799697876</v>
+        <v>2.68250584602356</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>2.496467113494873</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935292250664793</v>
+        <v>-0.06935259164652441</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.679741144180298</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0734133566970383</v>
+        <v>0.07341345219942963</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.679741144180298</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565840721130371</v>
+        <v>2.565840482711792</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250426325590773</v>
+        <v>-0.04250443741575582</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565840721130371</v>
+        <v>2.565840482711792</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834365844727</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854463275870208</v>
+        <v>0.3854463634027958</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834365844727</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7194,10 +7194,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.560006141662598</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454655740082078</v>
+        <v>0.00145485704413173</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.560006141662598</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.00205135345459</v>
+        <v>4.002051830291748</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699396708196</v>
+        <v>0.1241699230391513</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.00205135345459</v>
+        <v>4.002051830291748</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.176385402679443</v>
+        <v>4.17638635635376</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356117246580737</v>
+        <v>0.0435612864237449</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.176385402679443</v>
+        <v>4.17638635635376</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.406353950500488</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506401484726586</v>
+        <v>0.05506388809886431</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.406353950500488</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097488880157471</v>
+        <v>5.097488403320312</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568496170350731</v>
+        <v>0.1568493836298717</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097488880157471</v>
+        <v>5.097488403320312</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571537017822</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.0288214196747697</v>
+        <v>-0.02882142237082763</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571537017822</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772733688354492</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592278326681819</v>
+        <v>-0.03592220880918029</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772733688354492</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.06273078918457</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702847435166309</v>
+        <v>0.2702840090465197</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.06273078918457</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484796689881163</v>
+        <v>-0.01484781076548469</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715785503387451</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301665282311129</v>
+        <v>-0.04301664938883587</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715785503387451</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.55067253112793</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888718832462622</v>
+        <v>-0.02888710249012416</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.55067253112793</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228055000305176</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.122036107404736</v>
+        <v>0.1220363441559658</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228055000305176</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850455760955811</v>
+        <v>5.850457191467285</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.0606287579879855</v>
+        <v>-0.06062888790395171</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850455760955811</v>
+        <v>5.850457191467285</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047036170959473</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360087111769672</v>
+        <v>0.03360045538057688</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047036170959473</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935434818267822</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469147235425563</v>
+        <v>0.146914667857688</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935434818267822</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>6.943833827972412</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211028569177319</v>
+        <v>0.001211235080261108</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042296886444092</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240502996866476</v>
+        <v>-0.2240500250890657</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042296886444092</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.302005767822266</v>
+        <v>3.30200457572937</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831362562963657</v>
+        <v>-0.1831368402774747</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.302005767822266</v>
+        <v>3.30200457572937</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>3.555529832839966</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677880744130383</v>
+        <v>0.07677919618103357</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819418430328369</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421907087205204</v>
+        <v>0.07421920498347312</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819418430328369</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445835590362549</v>
+        <v>4.445837020874023</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640086642779561</v>
+        <v>0.1640088934931905</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445835590362549</v>
+        <v>4.445837020874023</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481491088867188</v>
+        <v>4.481489658355713</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019976847981169</v>
+        <v>0.008019330738912256</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481491088867188</v>
+        <v>4.481489658355713</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357764720916748</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507481618085182</v>
+        <v>-0.2507480822462205</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357764720916748</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070911884307861</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123872145602557</v>
+        <v>0.2123878988483392</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070911884307861</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182209968566895</v>
+        <v>4.182210922241211</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.0273398411515744</v>
+        <v>0.02733971441168226</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182209968566895</v>
+        <v>4.182210922241211</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.156326293945312</v>
+        <v>4.156324863433838</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188994530671899</v>
+        <v>-0.006189563197233738</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.156326293945312</v>
+        <v>4.156324863433838</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>4.319095611572266</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916182371534838</v>
+        <v>0.03916218137096039</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987790584564209</v>
+        <v>4.987790107727051</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548229150566363</v>
+        <v>0.1548228046545519</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987790584564209</v>
+        <v>4.987790107727051</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381810665130615</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899691734969516</v>
+        <v>0.07899673370009652</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381810665130615</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842669486999512</v>
+        <v>5.842668056488037</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563267096236871</v>
+        <v>0.08563269372395554</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842669486999512</v>
+        <v>5.842668056488037</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870726585388184</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480210260927838</v>
+        <v>0.004802430236670041</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870726585388184</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8346,10 +8346,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710044384002686</v>
+        <v>6.710042953491211</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429665964522182</v>
+        <v>0.1429662599486818</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710044384002686</v>
+        <v>6.710042953491211</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395682257433085</v>
+        <v>-0.02395654342885645</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.261863708496094</v>
+        <v>7.261862754821777</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088011580457702</v>
+        <v>0.1088009317019811</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.261863708496094</v>
+        <v>7.261862754821777</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8454,10 +8454,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.820675849914551</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146573116753359</v>
+        <v>0.2146572085391054</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.820675849914551</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>9.443389892578125</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059708952683108</v>
+        <v>0.07059732102863103</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399799346924</v>
+        <v>10.55399513244629</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.117606930723466</v>
+        <v>0.1176066277577954</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399799346924</v>
+        <v>10.55399513244629</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8562,10 +8562,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.29795074462891</v>
+        <v>13.29794883728027</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599917825318532</v>
+        <v>0.2599919433730087</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.29795074462891</v>
+        <v>13.29794883728027</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>13.45708179473877</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196658441332676</v>
+        <v>0.01196672956150757</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -8670,10 +8670,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32877922058105</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921175375168209</v>
+        <v>0.06921152424538901</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32877922058105</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799800872803</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556746123653708</v>
+        <v>-0.02556732362456904</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799800872803</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998199561433103</v>
+        <v>-0.004998126501084554</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.6441125869751</v>
+        <v>13.64411067962646</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.0557939828648184</v>
+        <v>0.05579383527242676</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.6441125869751</v>
+        <v>13.64411067962646</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>13.28432464599609</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636946438879895</v>
+        <v>-0.02636932828224614</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762302398682</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244546873627026</v>
+        <v>0.124454830941596</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762302398682</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.16670799255371</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228129943304796</v>
+        <v>0.08228103355163019</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.16670799255371</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.9112720489502</v>
+        <v>19.91127586364746</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316219268710247</v>
+        <v>0.2316223081379092</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.9112720489502</v>
+        <v>19.91127586364746</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.41007041931152</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.0251717533870518</v>
+        <v>-0.0251720359416866</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.41007041931152</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683662414551</v>
+        <v>22.28683090209961</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099828948495</v>
+        <v>0.1482098009269623</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683662414551</v>
+        <v>22.28683090209961</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>20.62515449523926</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455890474406701</v>
+        <v>-0.07455866714113257</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487976074219</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341668361304334</v>
+        <v>0.2341667436536166</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487976074219</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -9102,10 +9102,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.53271102905273</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780539093935128</v>
+        <v>0.2780537054365424</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.53271102905273</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -9138,10 +9138,10 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981033634665004</v>
+        <v>-0.09981006661035974</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -9174,10 +9174,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.38160705566406</v>
+        <v>24.38161087036133</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674543610323084</v>
+        <v>-0.167454284996934</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.38160705566406</v>
+        <v>24.38161087036133</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9210,10 +9210,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103637695312</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124858483746885</v>
+        <v>-0.004124936067363305</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103637695312</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9246,10 +9246,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.1742992401123</v>
+        <v>27.17429351806641</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.119157305241937</v>
+        <v>0.1191569816697338</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.1742992401123</v>
+        <v>27.17429351806641</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9282,10 +9282,10 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.47107124328613</v>
+        <v>18.4710750579834</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202742385341527</v>
+        <v>-0.320273955026533</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.47107124328613</v>
+        <v>18.4710750579834</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59555816650391</v>
+        <v>18.59556579589844</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739561640910274</v>
+        <v>0.006739766771790112</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59555816650391</v>
+        <v>18.59556579589844</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9354,10 +9354,10 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013580322266</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879708737784411</v>
+        <v>-0.1879711556529652</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013580322266</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247398376465</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981663848721067</v>
+        <v>0.1981661828865631</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247398376465</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538608551025</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689701420047741</v>
+        <v>-0.1689700016846472</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538608551025</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>12.09545516967773</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.195534115260649</v>
+        <v>-0.1955341662868347</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.44858264923096</v>
+        <v>13.44858455657959</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707366172873</v>
+        <v>0.1118708943086355</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.44858264923096</v>
+        <v>13.44858455657959</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>16.86660575866699</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541548948752226</v>
+        <v>0.2541547170044127</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189521789551</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368685443762311</v>
+        <v>0.336868675327757</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189521789551</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863372802734</v>
+        <v>23.13863945007324</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883092769912784</v>
+        <v>0.1883094544534847</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863372802734</v>
+        <v>23.13863945007324</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68914413452148</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966628825185215</v>
+        <v>0.1966624217283688</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68914413452148</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.66123199462891</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008053544630072</v>
+        <v>-0.001007984799151096</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.66123199462891</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71433639526367</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634366105814382</v>
+        <v>0.3634365666879342</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71433639526367</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182104602933247</v>
+        <v>0.1182105733971262</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.2039794921875</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619630133525821</v>
+        <v>0.05619646510531018</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.2039794921875</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36947250366211</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779493598029</v>
+        <v>-0.1185781635581729</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36947250366211</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>40.65856552124023</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250726204228019</v>
+        <v>-0.06250717958217422</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.242417441765066</v>
+        <v>0.2424173645114505</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -10074,10 +10074,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.88335418701172</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858093057587894</v>
+        <v>0.2858095100706863</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.88335418701172</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09910583496094</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421813782406502</v>
+        <v>0.1421813644892354</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09910583496094</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>86.15633392333984</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376030793594532</v>
+        <v>-0.04376038890822365</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711796833401</v>
+        <v>0.2688710911304248</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10218,10 +10218,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429881861628</v>
+        <v>0.1269431366228349</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968688964844</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277639146240565</v>
+        <v>-0.05277657397651536</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968688964844</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.0403671264648</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008192895097527</v>
+        <v>0.02008212771048568</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.0403671264648</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>121.1150283813477</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174282162006334</v>
+        <v>0.0174281509928309</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047088623047</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321453028446558</v>
+        <v>0.09321465627039194</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047088623047</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10398,10 +10398,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>137.8800201416016</v>
+        <v>137.8800506591797</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135284406682982</v>
+        <v>0.0413529545447211</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>137.8800201416016</v>
+        <v>137.8800506591797</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -10434,10 +10434,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398345947266</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691450021882</v>
+        <v>-0.02857701884229569</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398345947266</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>119.7569427490234</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058900206097576</v>
+        <v>-0.1058901224691788</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942916870117</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.0403930563602144</v>
+        <v>0.04039312006754003</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942916870117</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.132324990602127</v>
+        <v>-0.1323249824993521</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982481462220356</v>
+        <v>0.004982410538207693</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -10650,10 +10650,10 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.6035003662109</v>
+        <v>157.603515625</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515691786884</v>
+        <v>0.1692516823827925</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.6035003662109</v>
+        <v>157.603515625</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348907470703</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258307069145082</v>
+        <v>0.1258307915494528</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348907470703</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.0207454681313487</v>
+        <v>-0.02074555055982463</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125119707459349</v>
+        <v>0.07125110299903326</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -10794,10 +10794,10 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.0852718395616765</v>
+        <v>0.08527167560685012</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258828209996035</v>
+        <v>-0.1258826889444383</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293472316669725</v>
+        <v>-0.07293464314527709</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925888464382</v>
+        <v>-0.01569258749190239</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234709050238</v>
+        <v>0.1443234582488593</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797470065579535</v>
+        <v>0.05797461957992356</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11657,7 +11657,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.755945312720088</v>
+        <v>4.755945221301799</v>
       </c>
     </row>
     <row r="3">
@@ -11670,7 +11670,7 @@
         <v>3.408469136214709</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.891645733695004</v>
+        <v>3.891645895145746</v>
       </c>
     </row>
     <row r="4">
@@ -11709,7 +11709,7 @@
         <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.06459141507334</v>
+        <v>12.06459049542588</v>
       </c>
     </row>
     <row r="7">
@@ -11722,7 +11722,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791788925788385</v>
+        <v>-8.791787481952579</v>
       </c>
     </row>
     <row r="8">
@@ -11735,7 +11735,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54463275870208</v>
+        <v>38.54463634027958</v>
       </c>
     </row>
     <row r="9">
@@ -11748,7 +11748,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02742385341527</v>
+        <v>-32.0273955026533</v>
       </c>
     </row>
     <row r="10">
@@ -11761,7 +11761,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.755945312720088</v>
+        <v>4.755945221301799</v>
       </c>
     </row>
     <row r="11">
@@ -11774,7 +11774,7 @@
         <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.34711369180711</v>
+        <v>13.34711191641553</v>
       </c>
     </row>
     <row r="12">
@@ -11787,7 +11787,7 @@
         <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.02931179138729888</v>
+        <v>-0.02931161959291562</v>
       </c>
     </row>
     <row r="13">
@@ -11800,7 +11800,7 @@
         <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1936187715291005</v>
+        <v>0.1936184987708893</v>
       </c>
     </row>
     <row r="14">
@@ -11813,7 +11813,7 @@
         <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3563276242742608</v>
+        <v>0.3563276648225666</v>
       </c>
     </row>
     <row r="15">
@@ -11826,7 +11826,7 @@
         <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6778716925034239</v>
+        <v>0.67787179075673</v>
       </c>
     </row>
     <row r="16">
@@ -11839,7 +11839,7 @@
         <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.543695379374659</v>
+        <v>2.543695603216068</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T17:33:58</t>
+          <t>2026-10-20T17:44:08</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296821150432</v>
+        <v>27.82296668891937</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>117</v>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02055318845689392</v>
+        <v>0.0205531874786004</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>27.65203031222323</v>
+        <v>27.65202884382967</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.462030312223231</v>
+        <v>6.462028843829668</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -6943,7 +6943,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.68250584602356</v>
+        <v>2.682506322860718</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285933094947112</v>
+        <v>0.02285951277100851</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.68250584602356</v>
+        <v>2.682506322860718</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.496467113494873</v>
+        <v>2.496467590332031</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935259164652441</v>
+        <v>-0.06935257931854133</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.496467113494873</v>
+        <v>2.496467590332031</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>2.679741382598877</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341345219942963</v>
+        <v>0.07341324717236564</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565840482711792</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250443741575582</v>
+        <v>-0.04250434844501383</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565840482711792</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834365844727</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854463634027958</v>
+        <v>0.3854463275870208</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834365844727</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7194,10 +7194,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560006141662598</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.00145485704413173</v>
+        <v>0.001454588671257362</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560006141662598</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>4.002051830291748</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699230391513</v>
+        <v>0.124170148900882</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.17638635635376</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.0435612864237449</v>
+        <v>0.04356152472008823</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.17638635635376</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406352996826172</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506388809886431</v>
+        <v>0.0550633046523048</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406352996826172</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097488403320312</v>
+        <v>5.097489356994629</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568493836298717</v>
+        <v>0.1568499756297945</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097488403320312</v>
+        <v>5.097489356994629</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.950571537017822</v>
+        <v>4.950572967529297</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882142237082763</v>
+        <v>-0.0288213234351804</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.950571537017822</v>
+        <v>4.950572967529297</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772736549377441</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592220880918029</v>
+        <v>-0.03592239106832296</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772736549377441</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>6.062730312347412</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840090465197</v>
+        <v>0.2702838821342943</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786933898926</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301664938883587</v>
+        <v>-0.04301648971692962</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786933898926</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>5.550673484802246</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888710249012416</v>
+        <v>-0.02888726451950696</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363441559658</v>
+        <v>0.1220361723436048</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850457191467285</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062888790395171</v>
+        <v>-0.06062882062502617</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850457191467285</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047037124633789</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360045538057688</v>
+        <v>0.03360086564046827</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047037124633789</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.146914667857688</v>
+        <v>0.1469144638086999</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835735321045</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211235080261108</v>
+        <v>0.001211372421218604</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835735321045</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>5.20948314666748</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497684599418704</v>
+        <v>-0.2497686660171804</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240500250890657</v>
+        <v>-0.2240499335565385</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7842,10 +7842,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.30200457572937</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831368402774747</v>
+        <v>-0.183136818674309</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.30200457572937</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530786514282</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677919618103357</v>
+        <v>0.07677932950184241</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530786514282</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819418430328369</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421920498347312</v>
+        <v>0.0742187827420373</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819418430328369</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445837020874023</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640088934931905</v>
+        <v>0.1640089139689633</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445837020874023</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>4.481489658355713</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019330738912256</v>
+        <v>0.008019438853789751</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357764720916748</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480822462205</v>
+        <v>-0.2507479758447347</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357764720916748</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123878988483392</v>
+        <v>0.2123873006459764</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182210922241211</v>
+        <v>4.182209014892578</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733971441168226</v>
+        <v>0.02733960688604764</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182210922241211</v>
+        <v>4.182209014892578</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.156324863433838</v>
+        <v>4.156327247619629</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189563197233738</v>
+        <v>-0.006188539879471766</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.156324863433838</v>
+        <v>4.156327247619629</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.319095611572266</v>
+        <v>4.319097995758057</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916218137096039</v>
+        <v>0.03916215890643548</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.319095611572266</v>
+        <v>4.319097995758057</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987790107727051</v>
+        <v>4.987791538238525</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548228046545519</v>
+        <v>0.1548224983867503</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987790107727051</v>
+        <v>4.987791538238525</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899673370009652</v>
+        <v>0.0789967110436296</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842668056488037</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563269372395554</v>
+        <v>0.0856324937591233</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842668056488037</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802430236670041</v>
+        <v>0.004802185006011594</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8346,10 +8346,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710042953491211</v>
+        <v>6.710043907165527</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429662599486818</v>
+        <v>0.1429666080643739</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710042953491211</v>
+        <v>6.710043907165527</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.54929256439209</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395654342885645</v>
+        <v>-0.02395682427677925</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.54929256439209</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.261862754821777</v>
+        <v>7.261863231658936</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088009317019811</v>
+        <v>0.1088011659673027</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.261862754821777</v>
+        <v>7.261863231658936</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>8.820673942565918</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146572085391054</v>
+        <v>0.2146571287808294</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443387985229492</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059732102863103</v>
+        <v>0.07059710479247427</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443387985229492</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399513244629</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176066277577954</v>
+        <v>0.1176070554659563</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399513244629</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8562,10 +8562,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.29794883728027</v>
+        <v>13.29795265197754</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599919433730087</v>
+        <v>0.2599920771093882</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.29794883728027</v>
+        <v>13.29795265197754</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8598,10 +8598,10 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.45708179473877</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196672956150757</v>
+        <v>0.01196651098106316</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.45708179473877</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.465989112854</v>
+        <v>12.46599102020264</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364841033159564</v>
+        <v>-0.07364833424445749</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.465989112854</v>
+        <v>12.46599102020264</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8670,10 +8670,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.32877922058105</v>
+        <v>13.32878494262695</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921152424538901</v>
+        <v>0.06921181966408096</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.32877922058105</v>
+        <v>13.32878494262695</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799800872803</v>
+        <v>12.98799610137939</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556732362456904</v>
+        <v>-0.02556788504837204</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799800872803</v>
+        <v>12.98799610137939</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8742,10 +8742,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308330535889</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998126501084554</v>
+        <v>-0.004997906952991293</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308330535889</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.64411067962646</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579383527242676</v>
+        <v>0.05579383115505432</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.64411067962646</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8814,10 +8814,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636932828224614</v>
+        <v>-0.02636918664632026</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762302398682</v>
+        <v>14.93761825561523</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.124454830941596</v>
+        <v>0.1244542298225215</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762302398682</v>
+        <v>14.93761825561523</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228103355163019</v>
+        <v>0.08228150672390133</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.91127586364746</v>
+        <v>19.91127395629883</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316223081379092</v>
+        <v>0.2316220448510509</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.91127586364746</v>
+        <v>19.91127395629883</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>19.41006851196289</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.0251720359416866</v>
+        <v>-0.02517194256058053</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683090209961</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482098009269623</v>
+        <v>0.1482101939907232</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683090209961</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.62515449523926</v>
+        <v>20.62515640258789</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455866714113257</v>
+        <v>-0.07455889836317886</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.62515449523926</v>
+        <v>20.62515640258789</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45487976074219</v>
+        <v>25.45488357543945</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341667436536166</v>
+        <v>0.2341668144754319</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45487976074219</v>
+        <v>25.45488357543945</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -9102,10 +9102,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53269958496094</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537054365424</v>
+        <v>0.2780533640448715</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53269958496094</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>29.28561210632324</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981006661035974</v>
+        <v>-0.09980996105649786</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -9174,10 +9174,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.38161087036133</v>
+        <v>24.3816032409668</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.167454284996934</v>
+        <v>-0.1674545455137538</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.38161087036133</v>
+        <v>24.3816032409668</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9210,10 +9210,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124936067363305</v>
+        <v>-0.004124702671098213</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9246,10 +9246,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.17429351806641</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191569816697338</v>
+        <v>0.1191572266889214</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.17429351806641</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>18.4710750579834</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.320273955026533</v>
+        <v>-0.3202740504457099</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59556579589844</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739766771790112</v>
+        <v>0.006739663510413774</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59556579589844</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9354,10 +9354,10 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013580322266</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879711556529652</v>
+        <v>-0.1879711236481391</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013580322266</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981661828865631</v>
+        <v>0.1981660059320538</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.0353889465332</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689700016846472</v>
+        <v>-0.1689697210443043</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.0353889465332</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>12.09545516967773</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341662868347</v>
+        <v>-0.195534268339187</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.44858455657959</v>
+        <v>13.44858551025391</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708943086355</v>
+        <v>0.1118709731543095</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.44858455657959</v>
+        <v>13.44858551025391</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9534,10 +9534,10 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.86660575866699</v>
+        <v>16.86661148071289</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541547170044127</v>
+        <v>0.2541550535446946</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.86660575866699</v>
+        <v>16.86661148071289</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>14.56530284881592</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364413766930278</v>
+        <v>-0.1364416696577458</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.336868675327757</v>
+        <v>0.3368688062792828</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863945007324</v>
+        <v>23.13864135742188</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883094544534847</v>
+        <v>0.1883094360078374</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863945007324</v>
+        <v>23.13864135742188</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>27.68914031982422</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966624217283688</v>
+        <v>0.1966623230859119</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007984799151096</v>
+        <v>-0.001007915914793878</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9750,10 +9750,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365666879342</v>
+        <v>0.3634363347660106</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9786,10 +9786,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105733971262</v>
+        <v>0.11821058535379</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.58601760864258</v>
+        <v>46.58601379394531</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046522093279367</v>
+        <v>0.1046522187941983</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.58601760864258</v>
+        <v>46.58601379394531</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619646510531018</v>
+        <v>0.05619646970695968</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36946487426758</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185781635581729</v>
+        <v>-0.1185781727513269</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36946487426758</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>40.65856552124023</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250717958217422</v>
+        <v>-0.06250709712205382</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -9966,10 +9966,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307373046875</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468857564818131</v>
+        <v>0.1468859441272559</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307373046875</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.37888336181641</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893439166961034</v>
+        <v>0.05893405480119052</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.37888336181641</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424173645114505</v>
+        <v>0.2424176337275741</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858095100706863</v>
+        <v>0.2858094301189487</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.15633392333984</v>
+        <v>86.15635681152344</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376038890822365</v>
+        <v>-0.04376013487480812</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.15633392333984</v>
+        <v>86.15635681152344</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710911304248</v>
+        <v>0.2688708425967037</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431366228349</v>
+        <v>0.1269430579748985</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277657397651536</v>
+        <v>-0.05277651204904255</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008212771048568</v>
+        <v>0.02008206101966881</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174281509928309</v>
+        <v>0.01742821508364489</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321465627039194</v>
+        <v>0.09321446141964707</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10398,10 +10398,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>137.8800506591797</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.0413529545447211</v>
+        <v>0.04135295931038252</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>137.8800506591797</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857701884229569</v>
+        <v>-0.02857691133769347</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.7569427490234</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901224691788</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.7569427490234</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039312006754003</v>
+        <v>0.04039305893354816</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249824993521</v>
+        <v>-0.132324937470998</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982410538207693</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406354069759602</v>
+        <v>0.24063554742098</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>157.603515625</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516823827925</v>
+        <v>0.1692515500187184</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348907470703</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258307915494528</v>
+        <v>0.1258305979143173</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348907470703</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555055982463</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125110299903326</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258826889444383</v>
+        <v>-0.1258827644807442</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373090631056576</v>
+        <v>0.05373099736807707</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293464314527709</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.01569258749190239</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234582488593</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797461957992356</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11657,7 +11657,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.755945221301799</v>
+        <v>4.755945176363778</v>
       </c>
     </row>
     <row r="3">
@@ -11709,7 +11709,7 @@
         <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.06459049542588</v>
+        <v>12.06458916745936</v>
       </c>
     </row>
     <row r="7">
@@ -11722,7 +11722,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787481952579</v>
+        <v>-8.791785148593888</v>
       </c>
     </row>
     <row r="8">
@@ -11735,7 +11735,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54463634027958</v>
+        <v>38.54463275870208</v>
       </c>
     </row>
     <row r="9">
@@ -11748,7 +11748,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.0273955026533</v>
+        <v>-32.02740504457099</v>
       </c>
     </row>
     <row r="10">
@@ -11761,7 +11761,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.755945221301799</v>
+        <v>4.755945176363778</v>
       </c>
     </row>
     <row r="11">
@@ -11774,7 +11774,7 @@
         <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.34711191641553</v>
+        <v>13.34711112720858</v>
       </c>
     </row>
     <row r="12">
@@ -11787,7 +11787,7 @@
         <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.02931161959291562</v>
+        <v>-0.02931237411583189</v>
       </c>
     </row>
     <row r="13">
@@ -11800,7 +11800,7 @@
         <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1936184987708893</v>
+        <v>0.1936187840194536</v>
       </c>
     </row>
     <row r="14">
@@ -11813,7 +11813,7 @@
         <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3563276648225666</v>
+        <v>0.3563276825251428</v>
       </c>
     </row>
     <row r="15">
@@ -11826,7 +11826,7 @@
         <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.67787179075673</v>
+        <v>0.6778716976776478</v>
       </c>
     </row>
     <row r="16">
@@ -11839,7 +11839,7 @@
         <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.543695603216068</v>
+        <v>2.543695998330112</v>
       </c>
     </row>
   </sheetData>
